--- a/myprojects/FHEL/FHEL_Financial_Health_Analysis.xlsx
+++ b/myprojects/FHEL/FHEL_Financial_Health_Analysis.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="450" windowWidth="28800" windowHeight="13260" tabRatio="500" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="1350" windowWidth="28800" windowHeight="13260" tabRatio="500" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="HOME" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="277">
   <si>
     <t>FRESH &amp; HEALTHY ENTERPRISES LIMITED</t>
   </si>
@@ -430,9 +430,6 @@
     <t>Closing Cash &amp; Cash Equivalents</t>
   </si>
   <si>
-    <t>RATIO ANALYSIS  |  FY 2022-23 vs FY 2021-22</t>
-  </si>
-  <si>
     <t>Ratio</t>
   </si>
   <si>
@@ -571,9 +568,6 @@
     <t>BUSINESS ANALYSIS  |  FHEL FY 2022-23</t>
   </si>
   <si>
-    <t>All analysis based on FHEL 18th Annual Report 2022-23  |  Company is a loss-making Central Government PSU</t>
-  </si>
-  <si>
     <t>SWOT ANALYSIS</t>
   </si>
   <si>
@@ -592,9 +586,6 @@
     <t>First mover in specialized CA Storage for apples in India; 16 years of operational track record</t>
   </si>
   <si>
-    <t>Only 4 regular employees; extremely thin workforce for a multi-crore infrastructure business</t>
-  </si>
-  <si>
     <t>Agri Logistics Centre at Rai, Sonepat has diversified offering: CA, Chiller, Custom Bonded Warehouse</t>
   </si>
   <si>
@@ -748,12 +739,6 @@
     <t>Accumulated losses at INR 19,017 L; 6.6x the annual revenue; structural issue</t>
   </si>
   <si>
-    <t>Workforce</t>
-  </si>
-  <si>
-    <t>Staff count stable at 4; lean but risky for business continuity and scale</t>
-  </si>
-  <si>
     <t>MANAGEMENT &amp; GOVERNANCE</t>
   </si>
   <si>
@@ -857,6 +842,30 @@
   </si>
   <si>
     <t>Negligible inventory effect - services based</t>
+  </si>
+  <si>
+    <t>Anjani Kumar Mishra</t>
+  </si>
+  <si>
+    <t>https://inakm.github.io</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/inakmm</t>
+  </si>
+  <si>
+    <t>LinkedIn Profile</t>
+  </si>
+  <si>
+    <t>Portfolio</t>
+  </si>
+  <si>
+    <t>Extremely thin workforce for a multi-crore infrastructure business</t>
+  </si>
+  <si>
+    <t>RATIO ANALYSIS  |  FY 2022-23 vs 2021-22</t>
+  </si>
+  <si>
+    <t>Made by</t>
   </si>
 </sst>
 </file>
@@ -866,7 +875,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%;\(0.0%\);\-"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -966,6 +975,26 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="12">
     <fill>
@@ -1035,7 +1064,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -1071,11 +1100,92 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1154,6 +1264,39 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="13" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="13" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1195,29 +1338,9 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="13" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="13" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="13" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="13" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1500,253 +1623,284 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:H23"/>
+  <dimension ref="B2:H27"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="3" width="28" customWidth="1"/>
-    <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="5" max="8" width="18" customWidth="1"/>
+    <col min="4" max="4" width="36.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" customWidth="1"/>
+    <col min="7" max="7" width="5.7109375" customWidth="1"/>
+    <col min="8" max="8" width="6.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="33" t="s">
+      <c r="B2" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
     </row>
     <row r="3" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="34" t="s">
+      <c r="B3" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
     </row>
     <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="30" t="s">
+      <c r="B5" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="30"/>
-      <c r="D5" s="31" t="s">
+      <c r="C5" s="47"/>
+      <c r="D5" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="31"/>
-      <c r="F5" s="31"/>
-      <c r="G5" s="31"/>
-      <c r="H5" s="31"/>
+      <c r="E5" s="48"/>
+      <c r="F5" s="48"/>
+      <c r="G5" s="48"/>
+      <c r="H5" s="48"/>
     </row>
     <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="30" t="s">
+      <c r="B6" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="30"/>
-      <c r="D6" s="31" t="s">
+      <c r="C6" s="47"/>
+      <c r="D6" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="31"/>
-      <c r="F6" s="31"/>
-      <c r="G6" s="31"/>
-      <c r="H6" s="31"/>
+      <c r="E6" s="48"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="48"/>
+      <c r="H6" s="48"/>
     </row>
     <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="30" t="s">
+      <c r="B7" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="30"/>
-      <c r="D7" s="31" t="s">
+      <c r="C7" s="47"/>
+      <c r="D7" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="31"/>
-      <c r="F7" s="31"/>
-      <c r="G7" s="31"/>
-      <c r="H7" s="31"/>
+      <c r="E7" s="48"/>
+      <c r="F7" s="48"/>
+      <c r="G7" s="48"/>
+      <c r="H7" s="48"/>
     </row>
     <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="30" t="s">
+      <c r="B8" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="30"/>
-      <c r="D8" s="31" t="s">
+      <c r="C8" s="47"/>
+      <c r="D8" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="31"/>
-      <c r="F8" s="31"/>
-      <c r="G8" s="31"/>
-      <c r="H8" s="31"/>
+      <c r="E8" s="48"/>
+      <c r="F8" s="48"/>
+      <c r="G8" s="48"/>
+      <c r="H8" s="48"/>
     </row>
     <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="30" t="s">
+      <c r="B9" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="30"/>
-      <c r="D9" s="31" t="s">
+      <c r="C9" s="47"/>
+      <c r="D9" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="31"/>
-      <c r="F9" s="31"/>
-      <c r="G9" s="31"/>
-      <c r="H9" s="31"/>
+      <c r="E9" s="48"/>
+      <c r="F9" s="48"/>
+      <c r="G9" s="48"/>
+      <c r="H9" s="48"/>
     </row>
     <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="30" t="s">
+      <c r="B10" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="30"/>
-      <c r="D10" s="31" t="s">
+      <c r="C10" s="47"/>
+      <c r="D10" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="E10" s="31"/>
-      <c r="F10" s="31"/>
-      <c r="G10" s="31"/>
-      <c r="H10" s="31"/>
+      <c r="E10" s="48"/>
+      <c r="F10" s="48"/>
+      <c r="G10" s="48"/>
+      <c r="H10" s="48"/>
     </row>
     <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="30" t="s">
+      <c r="B11" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="30"/>
-      <c r="D11" s="31" t="s">
+      <c r="C11" s="47"/>
+      <c r="D11" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="E11" s="48"/>
+      <c r="F11" s="48"/>
+      <c r="G11" s="48"/>
+      <c r="H11" s="48"/>
+    </row>
+    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="47" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="47"/>
+      <c r="D12" s="48" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="48"/>
+      <c r="F12" s="48"/>
+      <c r="G12" s="48"/>
+      <c r="H12" s="48"/>
+    </row>
+    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="47" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="47"/>
+      <c r="D13" s="48" t="s">
+        <v>266</v>
+      </c>
+      <c r="E13" s="48"/>
+      <c r="F13" s="48"/>
+      <c r="G13" s="48"/>
+      <c r="H13" s="48"/>
+    </row>
+    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="47" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="47"/>
+      <c r="D14" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" s="48"/>
+      <c r="F14" s="48"/>
+      <c r="G14" s="48"/>
+      <c r="H14" s="48"/>
+    </row>
+    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="49" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="49"/>
+      <c r="D16" s="49"/>
+      <c r="E16" s="49"/>
+      <c r="F16" s="49"/>
+      <c r="G16" s="49"/>
+      <c r="H16" s="49"/>
+    </row>
+    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" s="46"/>
+      <c r="D18" s="46"/>
+      <c r="E18" s="46"/>
+      <c r="F18" s="46"/>
+      <c r="G18" s="46"/>
+      <c r="H18" s="46"/>
+    </row>
+    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19" s="44"/>
+      <c r="D19" s="45" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" s="45"/>
+      <c r="F19" s="45"/>
+      <c r="G19" s="45"/>
+      <c r="H19" s="45"/>
+    </row>
+    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="44" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" s="44"/>
+      <c r="D20" s="45" t="s">
+        <v>25</v>
+      </c>
+      <c r="E20" s="45"/>
+      <c r="F20" s="45"/>
+      <c r="G20" s="45"/>
+      <c r="H20" s="45"/>
+    </row>
+    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="44" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" s="44"/>
+      <c r="D21" s="45" t="s">
+        <v>27</v>
+      </c>
+      <c r="E21" s="45"/>
+      <c r="F21" s="45"/>
+      <c r="G21" s="45"/>
+      <c r="H21" s="45"/>
+    </row>
+    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="44" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22" s="44"/>
+      <c r="D22" s="45" t="s">
+        <v>29</v>
+      </c>
+      <c r="E22" s="45"/>
+      <c r="F22" s="45"/>
+      <c r="G22" s="45"/>
+      <c r="H22" s="45"/>
+    </row>
+    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="44" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="44"/>
+      <c r="D23" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="E23" s="45"/>
+      <c r="F23" s="45"/>
+      <c r="G23" s="45"/>
+      <c r="H23" s="45"/>
+    </row>
+    <row r="24" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="34" t="s">
+        <v>276</v>
+      </c>
+      <c r="C25" s="35"/>
+      <c r="D25" s="36" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="37" t="s">
+        <v>273</v>
+      </c>
+      <c r="C26" s="38"/>
+      <c r="D26" s="39" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="40" t="s">
         <v>272</v>
       </c>
-      <c r="E11" s="31"/>
-      <c r="F11" s="31"/>
-      <c r="G11" s="31"/>
-      <c r="H11" s="31"/>
-    </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="30" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="30"/>
-      <c r="D12" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="E12" s="31"/>
-      <c r="F12" s="31"/>
-      <c r="G12" s="31"/>
-      <c r="H12" s="31"/>
-    </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="30" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" s="30"/>
-      <c r="D13" s="31" t="s">
+      <c r="C27" s="41"/>
+      <c r="D27" s="42" t="s">
         <v>271</v>
       </c>
-      <c r="E13" s="31"/>
-      <c r="F13" s="31"/>
-      <c r="G13" s="31"/>
-      <c r="H13" s="31"/>
-    </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="30"/>
-      <c r="D14" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="E14" s="31"/>
-      <c r="F14" s="31"/>
-      <c r="G14" s="31"/>
-      <c r="H14" s="31"/>
-    </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="32" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" s="32"/>
-      <c r="D16" s="32"/>
-      <c r="E16" s="32"/>
-      <c r="F16" s="32"/>
-      <c r="G16" s="32"/>
-      <c r="H16" s="32"/>
-    </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="29" t="s">
-        <v>21</v>
-      </c>
-      <c r="C18" s="29"/>
-      <c r="D18" s="29"/>
-      <c r="E18" s="29"/>
-      <c r="F18" s="29"/>
-      <c r="G18" s="29"/>
-      <c r="H18" s="29"/>
-    </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="C19" s="27"/>
-      <c r="D19" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="28"/>
-      <c r="H19" s="28"/>
-    </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="27" t="s">
-        <v>24</v>
-      </c>
-      <c r="C20" s="27"/>
-      <c r="D20" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="28"/>
-    </row>
-    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="C21" s="27"/>
-      <c r="D21" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="E21" s="28"/>
-      <c r="F21" s="28"/>
-      <c r="G21" s="28"/>
-      <c r="H21" s="28"/>
-    </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="27" t="s">
-        <v>28</v>
-      </c>
-      <c r="C22" s="27"/>
-      <c r="D22" s="28" t="s">
-        <v>29</v>
-      </c>
-      <c r="E22" s="28"/>
-      <c r="F22" s="28"/>
-      <c r="G22" s="28"/>
-      <c r="H22" s="28"/>
-    </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="27" t="s">
-        <v>30</v>
-      </c>
-      <c r="C23" s="27"/>
-      <c r="D23" s="28" t="s">
-        <v>31</v>
-      </c>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="28"/>
-      <c r="H23" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="34">
@@ -1785,20 +1939,24 @@
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="D23:H23"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="D26" r:id="rId1"/>
+    <hyperlink ref="D27" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:U75"/>
+  <dimension ref="B1:Z45"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="30.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="20" customWidth="1"/>
-    <col min="5" max="5" width="43.28515625" customWidth="1"/>
+    <col min="5" max="5" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="4.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7.28515625" customWidth="1"/>
     <col min="8" max="8" width="1.85546875" customWidth="1"/>
@@ -1809,35 +1967,46 @@
     <col min="16" max="16" width="36.140625" bestFit="1" customWidth="1"/>
     <col min="17" max="18" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="2" customWidth="1"/>
+    <col min="23" max="23" width="30.5703125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="39.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="40" t="s">
+    <row r="1" spans="2:26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="57" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="I1" s="40" t="s">
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="I1" s="57" t="s">
         <v>61</v>
       </c>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="40"/>
-      <c r="M1" s="40"/>
-      <c r="N1" s="40"/>
-      <c r="P1" s="40" t="s">
+      <c r="J1" s="57"/>
+      <c r="K1" s="57"/>
+      <c r="L1" s="57"/>
+      <c r="M1" s="57"/>
+      <c r="N1" s="57"/>
+      <c r="P1" s="57" t="s">
         <v>99</v>
       </c>
-      <c r="Q1" s="40"/>
-      <c r="R1" s="40"/>
-      <c r="S1" s="40"/>
-      <c r="T1" s="40"/>
-      <c r="U1" s="40"/>
-    </row>
-    <row r="2" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="Q1" s="57"/>
+      <c r="R1" s="57"/>
+      <c r="S1" s="57"/>
+      <c r="T1" s="57"/>
+      <c r="U1" s="57"/>
+      <c r="W1" s="57" t="s">
+        <v>275</v>
+      </c>
+      <c r="X1" s="57"/>
+      <c r="Y1" s="57"/>
+      <c r="Z1" s="57"/>
+    </row>
+    <row r="2" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>33</v>
       </c>
@@ -1850,10 +2019,10 @@
       <c r="E2" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F2" s="39" t="s">
+      <c r="F2" s="56" t="s">
         <v>37</v>
       </c>
-      <c r="G2" s="39"/>
+      <c r="G2" s="56"/>
       <c r="I2" s="1" t="s">
         <v>33</v>
       </c>
@@ -1866,10 +2035,10 @@
       <c r="L2" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="M2" s="39" t="s">
+      <c r="M2" s="56" t="s">
         <v>37</v>
       </c>
-      <c r="N2" s="39"/>
+      <c r="N2" s="56"/>
       <c r="P2" s="1" t="s">
         <v>33</v>
       </c>
@@ -1882,38 +2051,56 @@
       <c r="S2" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="T2" s="39" t="s">
+      <c r="T2" s="56" t="s">
         <v>37</v>
       </c>
-      <c r="U2" s="39"/>
-    </row>
-    <row r="3" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="38" t="s">
+      <c r="U2" s="56"/>
+      <c r="W2" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z2" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="3" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="55" t="s">
         <v>38</v>
       </c>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="I3" s="38" t="s">
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="I3" s="55" t="s">
         <v>62</v>
       </c>
-      <c r="J3" s="38"/>
-      <c r="K3" s="38"/>
-      <c r="L3" s="38"/>
-      <c r="M3" s="38"/>
-      <c r="N3" s="38"/>
-      <c r="P3" s="38" t="s">
+      <c r="J3" s="55"/>
+      <c r="K3" s="55"/>
+      <c r="L3" s="55"/>
+      <c r="M3" s="55"/>
+      <c r="N3" s="55"/>
+      <c r="P3" s="55" t="s">
         <v>100</v>
       </c>
-      <c r="Q3" s="38"/>
-      <c r="R3" s="38"/>
-      <c r="S3" s="38"/>
-      <c r="T3" s="38"/>
-      <c r="U3" s="38"/>
-    </row>
-    <row r="4" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q3" s="55"/>
+      <c r="R3" s="55"/>
+      <c r="S3" s="55"/>
+      <c r="T3" s="55"/>
+      <c r="U3" s="55"/>
+      <c r="W3" s="55" t="s">
+        <v>133</v>
+      </c>
+      <c r="X3" s="55"/>
+      <c r="Y3" s="55"/>
+      <c r="Z3" s="55"/>
+    </row>
+    <row r="4" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="s">
         <v>39</v>
       </c>
@@ -1927,19 +2114,19 @@
         <f>C4-D4</f>
         <v>-117.75</v>
       </c>
-      <c r="F4" s="36">
+      <c r="F4" s="53">
         <f>(C4-D4)/ABS(D4)</f>
         <v>-0.17173735488011202</v>
       </c>
-      <c r="G4" s="36"/>
-      <c r="I4" s="41" t="s">
+      <c r="G4" s="53"/>
+      <c r="I4" s="58" t="s">
         <v>63</v>
       </c>
-      <c r="J4" s="41"/>
-      <c r="K4" s="41"/>
-      <c r="L4" s="41"/>
-      <c r="M4" s="41"/>
-      <c r="N4" s="41"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="58"/>
+      <c r="L4" s="58"/>
+      <c r="M4" s="58"/>
+      <c r="N4" s="58"/>
       <c r="P4" s="2" t="s">
         <v>101</v>
       </c>
@@ -1950,16 +2137,30 @@
         <v>-372.55</v>
       </c>
       <c r="S4" s="4">
-        <f>Q4-R4</f>
+        <f t="shared" ref="S4:S19" si="0">Q4-R4</f>
         <v>115.15000000000003</v>
       </c>
-      <c r="T4" s="36">
-        <f>(Q4-R4)/ABS(R4)</f>
+      <c r="T4" s="53">
+        <f t="shared" ref="T4:T19" si="1">(Q4-R4)/ABS(R4)</f>
         <v>0.30908602872097712</v>
       </c>
-      <c r="U4" s="36"/>
-    </row>
-    <row r="5" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U4" s="53"/>
+      <c r="W4" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="X4" s="27">
+        <f>J21/J41</f>
+        <v>2.6108227043008907</v>
+      </c>
+      <c r="Y4" s="27">
+        <f>K21/K41</f>
+        <v>1.4697792786179218</v>
+      </c>
+      <c r="Z4" s="14" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="5" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="6" t="s">
         <v>40</v>
       </c>
@@ -1973,11 +2174,11 @@
         <f>C5-D5</f>
         <v>33.24</v>
       </c>
-      <c r="F5" s="37">
+      <c r="F5" s="54">
         <f>(C5-D5)/ABS(D5)</f>
         <v>2.9157894736842107</v>
       </c>
-      <c r="G5" s="37"/>
+      <c r="G5" s="54"/>
       <c r="I5" s="6" t="s">
         <v>64</v>
       </c>
@@ -1988,14 +2189,14 @@
         <v>2489.5700000000002</v>
       </c>
       <c r="L5" s="8">
-        <f t="shared" ref="L5:L11" si="0">J5-K5</f>
+        <f t="shared" ref="L5:L11" si="2">J5-K5</f>
         <v>53.960000000000036</v>
       </c>
-      <c r="M5" s="37">
-        <f t="shared" ref="M5:M11" si="1">(J5-K5)/ABS(K5)</f>
+      <c r="M5" s="54">
+        <f t="shared" ref="M5:M11" si="3">(J5-K5)/ABS(K5)</f>
         <v>2.1674425704037256E-2</v>
       </c>
-      <c r="N5" s="37"/>
+      <c r="N5" s="54"/>
       <c r="P5" s="6" t="s">
         <v>102</v>
       </c>
@@ -2006,16 +2207,30 @@
         <v>455.54</v>
       </c>
       <c r="S5" s="8">
-        <f>Q5-R5</f>
+        <f t="shared" si="0"/>
         <v>-195.86</v>
       </c>
-      <c r="T5" s="37">
-        <f>(Q5-R5)/ABS(R5)</f>
+      <c r="T5" s="54">
+        <f t="shared" si="1"/>
         <v>-0.4299512666286166</v>
       </c>
-      <c r="U5" s="37"/>
-    </row>
-    <row r="6" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U5" s="54"/>
+      <c r="W5" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="X5" s="28">
+        <f>(J21-J14)/J41</f>
+        <v>2.6107539450613682</v>
+      </c>
+      <c r="Y5" s="28">
+        <f>(K21-K14)/K41</f>
+        <v>1.4697303381784368</v>
+      </c>
+      <c r="Z5" s="32" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="6" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="10" t="s">
         <v>41</v>
       </c>
@@ -2031,11 +2246,11 @@
         <f>C6-D6</f>
         <v>-84.509999999999991</v>
       </c>
-      <c r="F6" s="36">
+      <c r="F6" s="53">
         <f>(C6-D6)/ABS(D6)</f>
         <v>-0.12124124870882588</v>
       </c>
-      <c r="G6" s="36"/>
+      <c r="G6" s="53"/>
       <c r="I6" s="2" t="s">
         <v>65</v>
       </c>
@@ -2046,14 +2261,14 @@
         <v>0.73</v>
       </c>
       <c r="L6" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-0.22999999999999998</v>
       </c>
-      <c r="M6" s="36">
-        <f t="shared" si="1"/>
+      <c r="M6" s="53">
+        <f t="shared" si="3"/>
         <v>-0.31506849315068491</v>
       </c>
-      <c r="N6" s="36"/>
+      <c r="N6" s="53"/>
       <c r="P6" s="2" t="s">
         <v>103</v>
       </c>
@@ -2064,16 +2279,30 @@
         <v>-7.18</v>
       </c>
       <c r="S6" s="4">
-        <f>Q6-R6</f>
+        <f t="shared" si="0"/>
         <v>-5.15</v>
       </c>
-      <c r="T6" s="36">
-        <f>(Q6-R6)/ABS(R6)</f>
+      <c r="T6" s="53">
+        <f t="shared" si="1"/>
         <v>-0.71727019498607247</v>
       </c>
-      <c r="U6" s="36"/>
-    </row>
-    <row r="7" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="U6" s="53"/>
+      <c r="W6" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="X6" s="27">
+        <f>J16/J41</f>
+        <v>1.3262969711554993</v>
+      </c>
+      <c r="Y6" s="27">
+        <f>K16/K41</f>
+        <v>0.34556844320461994</v>
+      </c>
+      <c r="Z6" s="14" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="7" spans="2:26" x14ac:dyDescent="0.25">
       <c r="I7" s="6" t="s">
         <v>66</v>
       </c>
@@ -2084,14 +2313,14 @@
         <v>653.95000000000005</v>
       </c>
       <c r="L7" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>306.64999999999998</v>
       </c>
-      <c r="M7" s="37">
-        <f t="shared" si="1"/>
+      <c r="M7" s="54">
+        <f t="shared" si="3"/>
         <v>0.46891964217447812</v>
       </c>
-      <c r="N7" s="37"/>
+      <c r="N7" s="54"/>
       <c r="P7" s="6" t="s">
         <v>104</v>
       </c>
@@ -2102,24 +2331,30 @@
         <v>-1.5</v>
       </c>
       <c r="S7" s="8">
-        <f>Q7-R7</f>
+        <f t="shared" si="0"/>
         <v>-26.11</v>
       </c>
-      <c r="T7" s="37">
-        <f>(Q7-R7)/ABS(R7)</f>
+      <c r="T7" s="54">
+        <f t="shared" si="1"/>
         <v>-17.406666666666666</v>
       </c>
-      <c r="U7" s="37"/>
-    </row>
-    <row r="8" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="38" t="s">
+      <c r="U7" s="54"/>
+      <c r="W7" s="55" t="s">
+        <v>139</v>
+      </c>
+      <c r="X7" s="55"/>
+      <c r="Y7" s="55"/>
+      <c r="Z7" s="55"/>
+    </row>
+    <row r="8" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="55" t="s">
         <v>42</v>
       </c>
-      <c r="C8" s="38"/>
-      <c r="D8" s="38"/>
-      <c r="E8" s="38"/>
-      <c r="F8" s="38"/>
-      <c r="G8" s="38"/>
+      <c r="C8" s="55"/>
+      <c r="D8" s="55"/>
+      <c r="E8" s="55"/>
+      <c r="F8" s="55"/>
+      <c r="G8" s="55"/>
       <c r="I8" s="2" t="s">
         <v>67</v>
       </c>
@@ -2130,14 +2365,14 @@
         <v>0.13</v>
       </c>
       <c r="L8" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-0.12000000000000001</v>
       </c>
-      <c r="M8" s="36">
-        <f t="shared" si="1"/>
+      <c r="M8" s="53">
+        <f t="shared" si="3"/>
         <v>-0.92307692307692313</v>
       </c>
-      <c r="N8" s="36"/>
+      <c r="N8" s="53"/>
       <c r="P8" s="2" t="s">
         <v>105</v>
       </c>
@@ -2148,16 +2383,28 @@
         <v>6.79</v>
       </c>
       <c r="S8" s="4">
-        <f>Q8-R8</f>
+        <f t="shared" si="0"/>
         <v>6.3299999999999992</v>
       </c>
-      <c r="T8" s="36">
-        <f>(Q8-R8)/ABS(R8)</f>
+      <c r="T8" s="53">
+        <f t="shared" si="1"/>
         <v>0.93225331369661257</v>
       </c>
-      <c r="U8" s="36"/>
-    </row>
-    <row r="9" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U8" s="53"/>
+      <c r="W8" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="X8" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="Y8" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="Z8" s="14" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="9" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="6" t="s">
         <v>43</v>
       </c>
@@ -2168,14 +2415,14 @@
         <v>470.73</v>
       </c>
       <c r="E9" s="8">
-        <f t="shared" ref="E9:E14" si="2">C9-D9</f>
+        <f t="shared" ref="E9:E14" si="4">C9-D9</f>
         <v>-14.890000000000043</v>
       </c>
-      <c r="F9" s="37">
-        <f t="shared" ref="F9:F14" si="3">(C9-D9)/ABS(D9)</f>
+      <c r="F9" s="54">
+        <f t="shared" ref="F9:F14" si="5">(C9-D9)/ABS(D9)</f>
         <v>-3.1631720944065689E-2</v>
       </c>
-      <c r="G9" s="37"/>
+      <c r="G9" s="54"/>
       <c r="I9" s="6" t="s">
         <v>68</v>
       </c>
@@ -2186,14 +2433,14 @@
         <v>46.87</v>
       </c>
       <c r="L9" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.42000000000000171</v>
       </c>
-      <c r="M9" s="37">
-        <f t="shared" si="1"/>
+      <c r="M9" s="54">
+        <f t="shared" si="3"/>
         <v>8.9609558352891343E-3</v>
       </c>
-      <c r="N9" s="37"/>
+      <c r="N9" s="54"/>
       <c r="P9" s="6" t="s">
         <v>106</v>
       </c>
@@ -2204,16 +2451,30 @@
         <v>-0.86</v>
       </c>
       <c r="S9" s="8">
-        <f>Q9-R9</f>
+        <f t="shared" si="0"/>
         <v>8.9999999999999969E-2</v>
       </c>
-      <c r="T9" s="37">
-        <f>(Q9-R9)/ABS(R9)</f>
+      <c r="T9" s="54">
+        <f t="shared" si="1"/>
         <v>0.10465116279069764</v>
       </c>
-      <c r="U9" s="37"/>
-    </row>
-    <row r="10" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U9" s="54"/>
+      <c r="W9" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="X9" s="29">
+        <f>J42/J28</f>
+        <v>0.1134161254521539</v>
+      </c>
+      <c r="Y9" s="29">
+        <f>K42/K28</f>
+        <v>0.14604436273626273</v>
+      </c>
+      <c r="Z9" s="15" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="10" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
         <v>44</v>
       </c>
@@ -2224,14 +2485,14 @@
         <v>22.66</v>
       </c>
       <c r="E10" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>13.919999999999998</v>
       </c>
-      <c r="F10" s="36">
-        <f t="shared" si="3"/>
+      <c r="F10" s="53">
+        <f t="shared" si="5"/>
         <v>0.61429832303618703</v>
       </c>
-      <c r="G10" s="36"/>
+      <c r="G10" s="53"/>
       <c r="I10" s="2" t="s">
         <v>69</v>
       </c>
@@ -2245,11 +2506,11 @@
         <f>J10-K10</f>
         <v>-0.58999999999999986</v>
       </c>
-      <c r="M10" s="36">
-        <f t="shared" si="1"/>
+      <c r="M10" s="53">
+        <f t="shared" si="3"/>
         <v>-2.5563258232235698E-2</v>
       </c>
-      <c r="N10" s="36"/>
+      <c r="N10" s="53"/>
       <c r="P10" s="10" t="s">
         <v>107</v>
       </c>
@@ -2262,16 +2523,28 @@
         <v>80.240000000000009</v>
       </c>
       <c r="S10" s="4">
-        <f>Q10-R10</f>
+        <f t="shared" si="0"/>
         <v>-105.54999999999998</v>
       </c>
-      <c r="T10" s="36">
-        <f>(Q10-R10)/ABS(R10)</f>
+      <c r="T10" s="53">
+        <f t="shared" si="1"/>
         <v>-1.3154287138584244</v>
       </c>
-      <c r="U10" s="36"/>
-    </row>
-    <row r="11" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U10" s="53"/>
+      <c r="W10" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="X10" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="Y10" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z10" s="14" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="11" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="6" t="s">
         <v>45</v>
       </c>
@@ -2282,14 +2555,14 @@
         <v>6.79</v>
       </c>
       <c r="E11" s="8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>6.3299999999999992</v>
       </c>
-      <c r="F11" s="37">
-        <f t="shared" si="3"/>
+      <c r="F11" s="54">
+        <f t="shared" si="5"/>
         <v>0.93225331369661257</v>
       </c>
-      <c r="G11" s="37"/>
+      <c r="G11" s="54"/>
       <c r="I11" s="12" t="s">
         <v>70</v>
       </c>
@@ -2302,14 +2575,14 @@
         <v>3214.33</v>
       </c>
       <c r="L11" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>360.09000000000015</v>
       </c>
-      <c r="M11" s="37">
-        <f t="shared" si="1"/>
+      <c r="M11" s="54">
+        <f t="shared" si="3"/>
         <v>0.11202645652437682</v>
       </c>
-      <c r="N11" s="37"/>
+      <c r="N11" s="54"/>
       <c r="P11" s="6" t="s">
         <v>108</v>
       </c>
@@ -2320,16 +2593,22 @@
         <v>-31.64</v>
       </c>
       <c r="S11" s="8">
-        <f>Q11-R11</f>
+        <f t="shared" si="0"/>
         <v>76.62</v>
       </c>
-      <c r="T11" s="37">
-        <f>(Q11-R11)/ABS(R11)</f>
+      <c r="T11" s="54">
+        <f t="shared" si="1"/>
         <v>2.4216182048040458</v>
       </c>
-      <c r="U11" s="37"/>
-    </row>
-    <row r="12" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U11" s="54"/>
+      <c r="W11" s="55" t="s">
+        <v>148</v>
+      </c>
+      <c r="X11" s="55"/>
+      <c r="Y11" s="55"/>
+      <c r="Z11" s="55"/>
+    </row>
+    <row r="12" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="2" t="s">
         <v>46</v>
       </c>
@@ -2340,14 +2619,14 @@
         <v>455.54</v>
       </c>
       <c r="E12" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>-195.86</v>
       </c>
-      <c r="F12" s="36">
-        <f t="shared" si="3"/>
+      <c r="F12" s="53">
+        <f t="shared" si="5"/>
         <v>-0.4299512666286166</v>
       </c>
-      <c r="G12" s="36"/>
+      <c r="G12" s="53"/>
       <c r="P12" s="2" t="s">
         <v>109</v>
       </c>
@@ -2358,16 +2637,30 @@
         <v>-15.04</v>
       </c>
       <c r="S12" s="4">
-        <f>Q12-R12</f>
+        <f t="shared" si="0"/>
         <v>48.589999999999996</v>
       </c>
-      <c r="T12" s="36">
-        <f>(Q12-R12)/ABS(R12)</f>
+      <c r="T12" s="53">
+        <f t="shared" si="1"/>
         <v>3.2307180851063828</v>
       </c>
-      <c r="U12" s="36"/>
-    </row>
-    <row r="13" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U12" s="53"/>
+      <c r="W12" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="X12" s="30">
+        <f>(C6-C9)/C6</f>
+        <v>0.25580787879777317</v>
+      </c>
+      <c r="Y12" s="30">
+        <f>(D6-D9)/D6</f>
+        <v>0.32467290255939396</v>
+      </c>
+      <c r="Z12" s="14" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="13" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="6" t="s">
         <v>47</v>
       </c>
@@ -2378,22 +2671,22 @@
         <v>111.19</v>
       </c>
       <c r="E13" s="8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>-6.480000000000004</v>
       </c>
-      <c r="F13" s="37">
-        <f t="shared" si="3"/>
+      <c r="F13" s="54">
+        <f t="shared" si="5"/>
         <v>-5.8278622178253477E-2</v>
       </c>
-      <c r="G13" s="37"/>
-      <c r="I13" s="41" t="s">
+      <c r="G13" s="54"/>
+      <c r="I13" s="58" t="s">
         <v>71</v>
       </c>
-      <c r="J13" s="41"/>
-      <c r="K13" s="41"/>
-      <c r="L13" s="41"/>
-      <c r="M13" s="41"/>
-      <c r="N13" s="41"/>
+      <c r="J13" s="58"/>
+      <c r="K13" s="58"/>
+      <c r="L13" s="58"/>
+      <c r="M13" s="58"/>
+      <c r="N13" s="58"/>
       <c r="P13" s="6" t="s">
         <v>110</v>
       </c>
@@ -2404,36 +2697,50 @@
         <v>55.8</v>
       </c>
       <c r="S13" s="8">
-        <f>Q13-R13</f>
+        <f t="shared" si="0"/>
         <v>-155.98000000000002</v>
       </c>
-      <c r="T13" s="37">
-        <f>(Q13-R13)/ABS(R13)</f>
+      <c r="T13" s="54">
+        <f t="shared" si="1"/>
         <v>-2.7953405017921154</v>
       </c>
-      <c r="U13" s="37"/>
-    </row>
-    <row r="14" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U13" s="54"/>
+      <c r="W13" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="X13" s="31">
+        <f>(C16+C12+C11)/C6</f>
+        <v>2.5141625716291308E-2</v>
+      </c>
+      <c r="Y13" s="31">
+        <f>(D16+D12+D11)/D6</f>
+        <v>0.13264661999311361</v>
+      </c>
+      <c r="Z13" s="15" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="14" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="10" t="s">
         <v>48</v>
       </c>
       <c r="C14" s="4">
-        <f>C9+C10+C11+C12+C13</f>
+        <f>SUM(C9:C13)</f>
         <v>869.93000000000006</v>
       </c>
       <c r="D14" s="4">
-        <f>D9+D10+D11+D12+D13</f>
+        <f>SUM(D9:D13)</f>
         <v>1066.9100000000001</v>
       </c>
       <c r="E14" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>-196.98000000000002</v>
       </c>
-      <c r="F14" s="36">
-        <f t="shared" si="3"/>
+      <c r="F14" s="53">
+        <f t="shared" si="5"/>
         <v>-0.1846266320495637</v>
       </c>
-      <c r="G14" s="36"/>
+      <c r="G14" s="53"/>
       <c r="I14" s="2" t="s">
         <v>72</v>
       </c>
@@ -2444,14 +2751,14 @@
         <v>0.02</v>
       </c>
       <c r="L14" s="4">
-        <f t="shared" ref="L14:L22" si="4">J14-K14</f>
+        <f t="shared" ref="L14:L22" si="6">J14-K14</f>
         <v>0</v>
       </c>
-      <c r="M14" s="36">
-        <f t="shared" ref="M14:M22" si="5">(J14-K14)/ABS(K14)</f>
+      <c r="M14" s="53">
+        <f t="shared" ref="M14:M22" si="7">(J14-K14)/ABS(K14)</f>
         <v>0</v>
       </c>
-      <c r="N14" s="36"/>
+      <c r="N14" s="53"/>
       <c r="P14" s="2" t="s">
         <v>111</v>
       </c>
@@ -2462,16 +2769,30 @@
         <v>-0.01</v>
       </c>
       <c r="S14" s="4">
-        <f>Q14-R14</f>
+        <f t="shared" si="0"/>
         <v>89.54</v>
       </c>
-      <c r="T14" s="36">
-        <f>(Q14-R14)/ABS(R14)</f>
+      <c r="T14" s="53">
+        <f t="shared" si="1"/>
         <v>8954</v>
       </c>
-      <c r="U14" s="36"/>
-    </row>
-    <row r="15" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="U14" s="53"/>
+      <c r="W14" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="X14" s="30">
+        <f>C18/C6</f>
+        <v>-0.42022431554372863</v>
+      </c>
+      <c r="Y14" s="30">
+        <f>D18/D6</f>
+        <v>-0.53062951910937695</v>
+      </c>
+      <c r="Z14" s="14" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="15" spans="2:26" x14ac:dyDescent="0.25">
       <c r="I15" s="6" t="s">
         <v>73</v>
       </c>
@@ -2482,14 +2803,14 @@
         <v>315.54000000000002</v>
       </c>
       <c r="L15" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>-44.980000000000018</v>
       </c>
-      <c r="M15" s="37">
-        <f t="shared" si="5"/>
+      <c r="M15" s="54">
+        <f t="shared" si="7"/>
         <v>-0.14254928059833941</v>
       </c>
-      <c r="N15" s="37"/>
+      <c r="N15" s="54"/>
       <c r="P15" s="6" t="s">
         <v>112</v>
       </c>
@@ -2500,16 +2821,30 @@
         <v>7.72</v>
       </c>
       <c r="S15" s="8">
-        <f>Q15-R15</f>
+        <f t="shared" si="0"/>
         <v>-17.43</v>
       </c>
-      <c r="T15" s="37">
-        <f>(Q15-R15)/ABS(R15)</f>
+      <c r="T15" s="54">
+        <f t="shared" si="1"/>
         <v>-2.2577720207253886</v>
       </c>
-      <c r="U15" s="37"/>
-    </row>
-    <row r="16" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U15" s="54"/>
+      <c r="W15" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="X15" s="31">
+        <f>C18/J28</f>
+        <v>-6.6127507398881971E-2</v>
+      </c>
+      <c r="Y15" s="31">
+        <f>D18/K28</f>
+        <v>-0.11110810713384518</v>
+      </c>
+      <c r="Z15" s="15" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="16" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="10" t="s">
         <v>49</v>
       </c>
@@ -2525,11 +2860,11 @@
         <f>C16-D16</f>
         <v>112.47000000000003</v>
       </c>
-      <c r="F16" s="36">
+      <c r="F16" s="53">
         <f>(C16-D16)/ABS(D16)</f>
         <v>0.30407981182577659</v>
       </c>
-      <c r="G16" s="36"/>
+      <c r="G16" s="53"/>
       <c r="I16" s="2" t="s">
         <v>74</v>
       </c>
@@ -2540,14 +2875,14 @@
         <v>141.22</v>
       </c>
       <c r="L16" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>244.55999999999997</v>
       </c>
-      <c r="M16" s="36">
-        <f t="shared" si="5"/>
+      <c r="M16" s="53">
+        <f t="shared" si="7"/>
         <v>1.7317660388047018</v>
       </c>
-      <c r="N16" s="36"/>
+      <c r="N16" s="53"/>
       <c r="P16" s="2" t="s">
         <v>113</v>
       </c>
@@ -2558,16 +2893,30 @@
         <v>0.57999999999999996</v>
       </c>
       <c r="S16" s="4">
-        <f>Q16-R16</f>
+        <f t="shared" si="0"/>
         <v>-0.51</v>
       </c>
-      <c r="T16" s="36">
-        <f>(Q16-R16)/ABS(R16)</f>
+      <c r="T16" s="53">
+        <f t="shared" si="1"/>
         <v>-0.8793103448275863</v>
       </c>
-      <c r="U16" s="36"/>
-    </row>
-    <row r="17" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U16" s="53"/>
+      <c r="W16" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="X16" s="30">
+        <f>(C16+C11)/(J28+J33)</f>
+        <v>-6.0419284308002842E-2</v>
+      </c>
+      <c r="Y16" s="30">
+        <f>(D16+D11)/(K28+K33)</f>
+        <v>-0.10658666110855056</v>
+      </c>
+      <c r="Z16" s="14" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="17" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="6" t="s">
         <v>50</v>
       </c>
@@ -2594,14 +2943,14 @@
         <v>5.44</v>
       </c>
       <c r="L17" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0.25</v>
       </c>
-      <c r="M17" s="37">
-        <f t="shared" si="5"/>
+      <c r="M17" s="54">
+        <f t="shared" si="7"/>
         <v>4.5955882352941173E-2</v>
       </c>
-      <c r="N17" s="37"/>
+      <c r="N17" s="54"/>
       <c r="P17" s="12" t="s">
         <v>114</v>
       </c>
@@ -2614,16 +2963,30 @@
         <v>97.65</v>
       </c>
       <c r="S17" s="8">
-        <f>Q17-R17</f>
+        <f t="shared" si="0"/>
         <v>-64.719999999999985</v>
       </c>
-      <c r="T17" s="37">
-        <f>(Q17-R17)/ABS(R17)</f>
+      <c r="T17" s="54">
+        <f t="shared" si="1"/>
         <v>-0.6627752176139271</v>
       </c>
-      <c r="U17" s="37"/>
-    </row>
-    <row r="18" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U17" s="54"/>
+      <c r="W17" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="X17" s="29">
+        <f>C18/J22</f>
+        <v>-5.9393192626383616E-2</v>
+      </c>
+      <c r="Y17" s="29">
+        <f>D18/K22</f>
+        <v>-9.6952269611556618E-2</v>
+      </c>
+      <c r="Z17" s="15" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="18" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="10" t="s">
         <v>52</v>
       </c>
@@ -2639,11 +3002,11 @@
         <f>C18-D18</f>
         <v>112.47000000000003</v>
       </c>
-      <c r="F18" s="36">
+      <c r="F18" s="53">
         <f>(C18-D18)/ABS(D18)</f>
         <v>0.30407981182577659</v>
       </c>
-      <c r="G18" s="36"/>
+      <c r="G18" s="53"/>
       <c r="I18" s="2" t="s">
         <v>76</v>
       </c>
@@ -2654,14 +3017,14 @@
         <v>6.3</v>
       </c>
       <c r="L18" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0.70000000000000018</v>
       </c>
-      <c r="M18" s="36">
-        <f t="shared" si="5"/>
+      <c r="M18" s="53">
+        <f t="shared" si="7"/>
         <v>0.11111111111111115</v>
       </c>
-      <c r="N18" s="36"/>
+      <c r="N18" s="53"/>
       <c r="P18" s="2" t="s">
         <v>115</v>
       </c>
@@ -2672,16 +3035,22 @@
         <v>-3.03</v>
       </c>
       <c r="S18" s="4">
-        <f>Q18-R18</f>
+        <f t="shared" si="0"/>
         <v>11.24</v>
       </c>
-      <c r="T18" s="36">
-        <f>(Q18-R18)/ABS(R18)</f>
+      <c r="T18" s="53">
+        <f t="shared" si="1"/>
         <v>3.7095709570957101</v>
       </c>
-      <c r="U18" s="36"/>
-    </row>
-    <row r="19" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="U18" s="53"/>
+      <c r="W18" s="55" t="s">
+        <v>158</v>
+      </c>
+      <c r="X18" s="55"/>
+      <c r="Y18" s="55"/>
+      <c r="Z18" s="55"/>
+    </row>
+    <row r="19" spans="2:26" x14ac:dyDescent="0.25">
       <c r="I19" s="6" t="s">
         <v>77</v>
       </c>
@@ -2692,14 +3061,14 @@
         <v>25.82</v>
       </c>
       <c r="L19" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>-8.2100000000000009</v>
       </c>
-      <c r="M19" s="37">
-        <f t="shared" si="5"/>
+      <c r="M19" s="54">
+        <f t="shared" si="7"/>
         <v>-0.31797056545313712</v>
       </c>
-      <c r="N19" s="37"/>
+      <c r="N19" s="54"/>
       <c r="P19" s="12" t="s">
         <v>116</v>
       </c>
@@ -2712,16 +3081,30 @@
         <v>94.62</v>
       </c>
       <c r="S19" s="8">
-        <f>Q19-R19</f>
+        <f t="shared" si="0"/>
         <v>-53.479999999999983</v>
       </c>
-      <c r="T19" s="37">
-        <f>(Q19-R19)/ABS(R19)</f>
+      <c r="T19" s="54">
+        <f t="shared" si="1"/>
         <v>-0.56520820122595627</v>
       </c>
-      <c r="U19" s="37"/>
-    </row>
-    <row r="20" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U19" s="54"/>
+      <c r="W19" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="X19" s="28">
+        <f>C4/((K15+J15)/2)</f>
+        <v>1.9378604333731444</v>
+      </c>
+      <c r="Y19" s="28">
+        <f>D4/((L15+K15)/2)</f>
+        <v>5.0683027794204607</v>
+      </c>
+      <c r="Z19" s="15" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="20" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="2" t="s">
         <v>53</v>
       </c>
@@ -2735,11 +3118,11 @@
         <f>C20-D20</f>
         <v>1.0000000000000002E-2</v>
       </c>
-      <c r="F20" s="36">
+      <c r="F20" s="53">
         <f>(C20-D20)/ABS(D20)</f>
         <v>0.20000000000000004</v>
       </c>
-      <c r="G20" s="36"/>
+      <c r="G20" s="53"/>
       <c r="I20" s="2" t="s">
         <v>78</v>
       </c>
@@ -2750,16 +3133,30 @@
         <v>106.3</v>
       </c>
       <c r="L20" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>-33.549999999999997</v>
       </c>
-      <c r="M20" s="36">
-        <f t="shared" si="5"/>
+      <c r="M20" s="53">
+        <f t="shared" si="7"/>
         <v>-0.31561618062088426</v>
       </c>
-      <c r="N20" s="36"/>
-    </row>
-    <row r="21" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N20" s="53"/>
+      <c r="W20" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="X20" s="33">
+        <f>365/X19</f>
+        <v>188.352057616792</v>
+      </c>
+      <c r="Y20" s="33">
+        <f>365/Y19</f>
+        <v>72.016218423662565</v>
+      </c>
+      <c r="Z20" s="14" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="21" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="12" t="s">
         <v>54</v>
       </c>
@@ -2775,11 +3172,11 @@
         <f>C21-D21</f>
         <v>112.48000000000002</v>
       </c>
-      <c r="F21" s="37">
+      <c r="F21" s="54">
         <f>(C21-D21)/ABS(D21)</f>
         <v>0.30406574394463665</v>
       </c>
-      <c r="G21" s="37"/>
+      <c r="G21" s="54"/>
       <c r="I21" s="12" t="s">
         <v>79</v>
       </c>
@@ -2792,24 +3189,38 @@
         <v>600.64</v>
       </c>
       <c r="L21" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>158.76999999999998</v>
       </c>
-      <c r="M21" s="37">
-        <f t="shared" si="5"/>
+      <c r="M21" s="54">
+        <f t="shared" si="7"/>
         <v>0.26433470964304739</v>
       </c>
-      <c r="N21" s="37"/>
-      <c r="P21" s="38" t="s">
+      <c r="N21" s="54"/>
+      <c r="P21" s="55" t="s">
         <v>117</v>
       </c>
-      <c r="Q21" s="38"/>
-      <c r="R21" s="38"/>
-      <c r="S21" s="38"/>
-      <c r="T21" s="38"/>
-      <c r="U21" s="38"/>
-    </row>
-    <row r="22" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="Q21" s="55"/>
+      <c r="R21" s="55"/>
+      <c r="S21" s="55"/>
+      <c r="T21" s="55"/>
+      <c r="U21" s="55"/>
+      <c r="W21" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="X21" s="28">
+        <f>C4/(J21-J41)</f>
+        <v>1.2120416613309428</v>
+      </c>
+      <c r="Y21" s="28">
+        <f>D4/(K21-K41)</f>
+        <v>3.5714136889259303</v>
+      </c>
+      <c r="Z21" s="15" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="22" spans="2:26" x14ac:dyDescent="0.25">
       <c r="I22" s="10" t="s">
         <v>80</v>
       </c>
@@ -2822,14 +3233,14 @@
         <v>3814.97</v>
       </c>
       <c r="L22" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>518.86000000000013</v>
       </c>
-      <c r="M22" s="36">
-        <f t="shared" si="5"/>
+      <c r="M22" s="53">
+        <f t="shared" si="7"/>
         <v>0.136006311976241</v>
       </c>
-      <c r="N22" s="36"/>
+      <c r="N22" s="53"/>
       <c r="P22" s="2" t="s">
         <v>118</v>
       </c>
@@ -2840,24 +3251,38 @@
         <v>-98.83</v>
       </c>
       <c r="S22" s="4">
-        <f>Q22-R22</f>
+        <f t="shared" ref="S22:S27" si="8">Q22-R22</f>
         <v>-214.78000000000003</v>
       </c>
-      <c r="T22" s="36">
-        <f>(Q22-R22)/ABS(R22)</f>
+      <c r="T22" s="53">
+        <f t="shared" ref="T22:T27" si="9">(Q22-R22)/ABS(R22)</f>
         <v>-2.1732267530102201</v>
       </c>
-      <c r="U22" s="36"/>
-    </row>
-    <row r="23" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="38" t="s">
+      <c r="U22" s="53"/>
+      <c r="W22" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="X22" s="27">
+        <f>C4/J22</f>
+        <v>0.13103651966043892</v>
+      </c>
+      <c r="Y22" s="27">
+        <f>D4/K22</f>
+        <v>0.17972356270167264</v>
+      </c>
+      <c r="Z22" s="14" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="23" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="55" t="s">
         <v>55</v>
       </c>
-      <c r="C23" s="38"/>
-      <c r="D23" s="38"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="38"/>
-      <c r="G23" s="38"/>
+      <c r="C23" s="55"/>
+      <c r="D23" s="55"/>
+      <c r="E23" s="55"/>
+      <c r="F23" s="55"/>
+      <c r="G23" s="55"/>
       <c r="P23" s="6" t="s">
         <v>119</v>
       </c>
@@ -2868,16 +3293,22 @@
         <v>-444.55</v>
       </c>
       <c r="S23" s="8">
-        <f>Q23-R23</f>
+        <f t="shared" si="8"/>
         <v>137.90000000000003</v>
       </c>
-      <c r="T23" s="37">
-        <f>(Q23-R23)/ABS(R23)</f>
+      <c r="T23" s="54">
+        <f t="shared" si="9"/>
         <v>0.31020132718479371</v>
       </c>
-      <c r="U23" s="37"/>
-    </row>
-    <row r="24" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U23" s="54"/>
+      <c r="W23" s="55" t="s">
+        <v>167</v>
+      </c>
+      <c r="X23" s="55"/>
+      <c r="Y23" s="55"/>
+      <c r="Z23" s="55"/>
+    </row>
+    <row r="24" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="1" t="s">
         <v>56</v>
       </c>
@@ -2890,16 +3321,16 @@
       <c r="E24" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="F24" s="39"/>
-      <c r="G24" s="39"/>
-      <c r="I24" s="38" t="s">
+      <c r="F24" s="56"/>
+      <c r="G24" s="56"/>
+      <c r="I24" s="55" t="s">
         <v>81</v>
       </c>
-      <c r="J24" s="38"/>
-      <c r="K24" s="38"/>
-      <c r="L24" s="38"/>
-      <c r="M24" s="38"/>
-      <c r="N24" s="38"/>
+      <c r="J24" s="55"/>
+      <c r="K24" s="55"/>
+      <c r="L24" s="55"/>
+      <c r="M24" s="55"/>
+      <c r="N24" s="55"/>
       <c r="P24" s="2" t="s">
         <v>120</v>
       </c>
@@ -2910,16 +3341,28 @@
         <v>6.24</v>
       </c>
       <c r="S24" s="4">
-        <f>Q24-R24</f>
+        <f t="shared" si="8"/>
         <v>-5.2700000000000005</v>
       </c>
-      <c r="T24" s="36">
-        <f>(Q24-R24)/ABS(R24)</f>
+      <c r="T24" s="53">
+        <f t="shared" si="9"/>
         <v>-0.84455128205128205</v>
       </c>
-      <c r="U24" s="36"/>
-    </row>
-    <row r="25" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U24" s="53"/>
+      <c r="W24" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="X24" s="26">
+        <v>19017.05</v>
+      </c>
+      <c r="Y24" s="26">
+        <v>18759.61</v>
+      </c>
+      <c r="Z24" s="14" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="25" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="6" t="s">
         <v>58</v>
       </c>
@@ -2935,16 +3378,16 @@
         <f>C25-D25</f>
         <v>-6.8865023761620792E-2</v>
       </c>
-      <c r="F25" s="35"/>
-      <c r="G25" s="35"/>
-      <c r="I25" s="41" t="s">
+      <c r="F25" s="52"/>
+      <c r="G25" s="52"/>
+      <c r="I25" s="58" t="s">
         <v>82</v>
       </c>
-      <c r="J25" s="41"/>
-      <c r="K25" s="41"/>
-      <c r="L25" s="41"/>
-      <c r="M25" s="41"/>
-      <c r="N25" s="41"/>
+      <c r="J25" s="58"/>
+      <c r="K25" s="58"/>
+      <c r="L25" s="58"/>
+      <c r="M25" s="58"/>
+      <c r="N25" s="58"/>
       <c r="P25" s="6" t="s">
         <v>121</v>
       </c>
@@ -2955,16 +3398,30 @@
         <v>0.12</v>
       </c>
       <c r="S25" s="8">
-        <f>Q25-R25</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="T25" s="37">
-        <f>(Q25-R25)/ABS(R25)</f>
+      <c r="T25" s="54">
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="U25" s="37"/>
-    </row>
-    <row r="26" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U25" s="54"/>
+      <c r="W25" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="X25" s="25">
+        <f>J28</f>
+        <v>3892.4799999999996</v>
+      </c>
+      <c r="Y25" s="25">
+        <f>K28</f>
+        <v>3328.9200000000019</v>
+      </c>
+      <c r="Z25" s="15" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="26" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="2" t="s">
         <v>59</v>
       </c>
@@ -2980,8 +3437,8 @@
         <f>C26-D26</f>
         <v>-0.10750499427682231</v>
       </c>
-      <c r="F26" s="35"/>
-      <c r="G26" s="35"/>
+      <c r="F26" s="52"/>
+      <c r="G26" s="52"/>
       <c r="I26" s="2" t="s">
         <v>83</v>
       </c>
@@ -2995,11 +3452,11 @@
         <f>J26-K26</f>
         <v>821</v>
       </c>
-      <c r="M26" s="36">
+      <c r="M26" s="53">
         <f>(J26-K26)/ABS(K26)</f>
         <v>3.7238288762291807E-2</v>
       </c>
-      <c r="N26" s="36"/>
+      <c r="N26" s="53"/>
       <c r="P26" s="2" t="s">
         <v>122</v>
       </c>
@@ -3010,16 +3467,28 @@
         <v>7.06</v>
       </c>
       <c r="S26" s="4">
-        <f>Q26-R26</f>
+        <f t="shared" si="8"/>
         <v>4.13</v>
       </c>
-      <c r="T26" s="36">
-        <f>(Q26-R26)/ABS(R26)</f>
+      <c r="T26" s="53">
+        <f t="shared" si="9"/>
         <v>0.58498583569405105</v>
       </c>
-      <c r="U26" s="36"/>
-    </row>
-    <row r="27" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U26" s="53"/>
+      <c r="W26" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="X26" s="26">
+        <v>821</v>
+      </c>
+      <c r="Y26" s="26">
+        <v>546</v>
+      </c>
+      <c r="Z26" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="27" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="6" t="s">
         <v>60</v>
       </c>
@@ -3035,8 +3504,8 @@
         <f>C27-D27</f>
         <v>0.11040520356564831</v>
       </c>
-      <c r="F27" s="35"/>
-      <c r="G27" s="35"/>
+      <c r="F27" s="52"/>
+      <c r="G27" s="52"/>
       <c r="I27" s="6" t="s">
         <v>84</v>
       </c>
@@ -3050,11 +3519,11 @@
         <f>J27-K27</f>
         <v>-257.44000000000233</v>
       </c>
-      <c r="M27" s="37">
+      <c r="M27" s="54">
         <f>(J27-K27)/ABS(K27)</f>
         <v>-1.3753400419269417E-2</v>
       </c>
-      <c r="N27" s="37"/>
+      <c r="N27" s="54"/>
       <c r="P27" s="12" t="s">
         <v>123</v>
       </c>
@@ -3067,16 +3536,28 @@
         <v>-529.96</v>
       </c>
       <c r="S27" s="8">
-        <f>Q27-R27</f>
+        <f t="shared" si="8"/>
         <v>-78.019999999999868</v>
       </c>
-      <c r="T27" s="37">
-        <f>(Q27-R27)/ABS(R27)</f>
+      <c r="T27" s="54">
+        <f t="shared" si="9"/>
         <v>-0.14721865801192516</v>
       </c>
-      <c r="U27" s="37"/>
-    </row>
-    <row r="28" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="U27" s="54"/>
+      <c r="W27" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="X27" s="25">
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="Y27" s="25">
+        <v>82.99</v>
+      </c>
+      <c r="Z27" s="15" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="28" spans="2:26" x14ac:dyDescent="0.25">
       <c r="I28" s="10" t="s">
         <v>85</v>
       </c>
@@ -3092,32 +3573,32 @@
         <f>J28-K28</f>
         <v>563.55999999999767</v>
       </c>
-      <c r="M28" s="36">
+      <c r="M28" s="53">
         <f>(J28-K28)/ABS(K28)</f>
         <v>0.16929214279706251</v>
       </c>
-      <c r="N28" s="36"/>
-    </row>
-    <row r="29" spans="2:21" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N28" s="53"/>
+    </row>
+    <row r="29" spans="2:26" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="13"/>
-      <c r="P29" s="38" t="s">
+      <c r="P29" s="55" t="s">
         <v>124</v>
       </c>
-      <c r="Q29" s="38"/>
-      <c r="R29" s="38"/>
-      <c r="S29" s="38"/>
-      <c r="T29" s="38"/>
-      <c r="U29" s="38"/>
-    </row>
-    <row r="30" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="I30" s="41" t="s">
+      <c r="Q29" s="55"/>
+      <c r="R29" s="55"/>
+      <c r="S29" s="55"/>
+      <c r="T29" s="55"/>
+      <c r="U29" s="55"/>
+    </row>
+    <row r="30" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="I30" s="58" t="s">
         <v>86</v>
       </c>
-      <c r="J30" s="41"/>
-      <c r="K30" s="41"/>
-      <c r="L30" s="41"/>
-      <c r="M30" s="41"/>
-      <c r="N30" s="41"/>
+      <c r="J30" s="58"/>
+      <c r="K30" s="58"/>
+      <c r="L30" s="58"/>
+      <c r="M30" s="58"/>
+      <c r="N30" s="58"/>
       <c r="P30" s="2" t="s">
         <v>125</v>
       </c>
@@ -3131,13 +3612,13 @@
         <f>Q30-R30</f>
         <v>0.35000000000000142</v>
       </c>
-      <c r="T30" s="36">
+      <c r="T30" s="53">
         <f>(Q30-R30)/ABS(R30)</f>
         <v>2.8455284552845642E-2</v>
       </c>
-      <c r="U30" s="36"/>
-    </row>
-    <row r="31" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="U30" s="53"/>
+    </row>
+    <row r="31" spans="2:26" x14ac:dyDescent="0.25">
       <c r="I31" s="6" t="s">
         <v>87</v>
       </c>
@@ -3151,11 +3632,11 @@
         <f>J31-K31</f>
         <v>71.060000000000016</v>
       </c>
-      <c r="M31" s="37">
+      <c r="M31" s="54">
         <f>(J31-K31)/ABS(K31)</f>
         <v>1.1181746656176241</v>
       </c>
-      <c r="N31" s="37"/>
+      <c r="N31" s="54"/>
       <c r="P31" s="6" t="s">
         <v>126</v>
       </c>
@@ -3169,13 +3650,13 @@
         <f>Q31-R31</f>
         <v>275</v>
       </c>
-      <c r="T31" s="37">
+      <c r="T31" s="54">
         <f>(Q31-R31)/ABS(R31)</f>
         <v>0.50366300366300365</v>
       </c>
-      <c r="U31" s="37"/>
-    </row>
-    <row r="32" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="U31" s="54"/>
+    </row>
+    <row r="32" spans="2:26" x14ac:dyDescent="0.25">
       <c r="I32" s="2" t="s">
         <v>88</v>
       </c>
@@ -3189,11 +3670,11 @@
         <f>J32-K32</f>
         <v>2.0299999999999994</v>
       </c>
-      <c r="M32" s="36">
+      <c r="M32" s="53">
         <f>(J32-K32)/ABS(K32)</f>
         <v>0.14541547277936956</v>
       </c>
-      <c r="N32" s="36"/>
+      <c r="N32" s="53"/>
       <c r="P32" s="10" t="s">
         <v>127</v>
       </c>
@@ -3209,11 +3690,11 @@
         <f>Q32-R32</f>
         <v>275.34999999999991</v>
       </c>
-      <c r="T32" s="36">
+      <c r="T32" s="53">
         <f>(Q32-R32)/ABS(R32)</f>
         <v>0.51592655049653346</v>
       </c>
-      <c r="U32" s="36"/>
+      <c r="U32" s="53"/>
     </row>
     <row r="33" spans="9:21" x14ac:dyDescent="0.25">
       <c r="I33" s="12" t="s">
@@ -3231,11 +3712,11 @@
         <f>J33-K33</f>
         <v>73.090000000000032</v>
       </c>
-      <c r="M33" s="37">
+      <c r="M33" s="54">
         <f>(J33-K33)/ABS(K33)</f>
         <v>0.94297509998709894</v>
       </c>
-      <c r="N33" s="37"/>
+      <c r="N33" s="54"/>
     </row>
     <row r="34" spans="9:21" x14ac:dyDescent="0.25">
       <c r="P34" s="10" t="s">
@@ -3253,21 +3734,21 @@
         <f>Q34-R34</f>
         <v>143.85000000000002</v>
       </c>
-      <c r="T34" s="36">
+      <c r="T34" s="53">
         <f>(Q34-R34)/ABS(R34)</f>
         <v>1.4624847498983327</v>
       </c>
-      <c r="U34" s="36"/>
+      <c r="U34" s="53"/>
     </row>
     <row r="35" spans="9:21" x14ac:dyDescent="0.25">
-      <c r="I35" s="41" t="s">
+      <c r="I35" s="58" t="s">
         <v>90</v>
       </c>
-      <c r="J35" s="41"/>
-      <c r="K35" s="41"/>
-      <c r="L35" s="41"/>
-      <c r="M35" s="41"/>
-      <c r="N35" s="41"/>
+      <c r="J35" s="58"/>
+      <c r="K35" s="58"/>
+      <c r="L35" s="58"/>
+      <c r="M35" s="58"/>
+      <c r="N35" s="58"/>
       <c r="P35" s="6" t="s">
         <v>129</v>
       </c>
@@ -3281,11 +3762,11 @@
         <f>Q35-R35</f>
         <v>102.38</v>
       </c>
-      <c r="T35" s="37">
+      <c r="T35" s="54">
         <f>(Q35-R35)/ABS(R35)</f>
         <v>2.3121047877145435</v>
       </c>
-      <c r="U35" s="37"/>
+      <c r="U35" s="54"/>
     </row>
     <row r="36" spans="9:21" x14ac:dyDescent="0.25">
       <c r="I36" s="2" t="s">
@@ -3298,14 +3779,14 @@
         <v>8.7100000000000009</v>
       </c>
       <c r="L36" s="4">
-        <f t="shared" ref="L36:L43" si="6">J36-K36</f>
+        <f t="shared" ref="L36:L43" si="10">J36-K36</f>
         <v>19.64</v>
       </c>
-      <c r="M36" s="36">
-        <f t="shared" ref="M36:M43" si="7">(J36-K36)/ABS(K36)</f>
+      <c r="M36" s="53">
+        <f t="shared" ref="M36:M43" si="11">(J36-K36)/ABS(K36)</f>
         <v>2.2548794489092994</v>
       </c>
-      <c r="N36" s="36"/>
+      <c r="N36" s="53"/>
       <c r="P36" s="10" t="s">
         <v>130</v>
       </c>
@@ -3321,11 +3802,11 @@
         <f>Q36-R36</f>
         <v>246.23</v>
       </c>
-      <c r="T36" s="36">
+      <c r="T36" s="53">
         <f>(Q36-R36)/ABS(R36)</f>
         <v>1.7262338754907456</v>
       </c>
-      <c r="U36" s="36"/>
+      <c r="U36" s="53"/>
     </row>
     <row r="37" spans="9:21" x14ac:dyDescent="0.25">
       <c r="I37" s="6" t="s">
@@ -3338,14 +3819,14 @@
         <v>0.05</v>
       </c>
       <c r="L37" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="M37" s="37">
-        <f t="shared" si="7"/>
+      <c r="M37" s="54">
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="N37" s="37"/>
+      <c r="N37" s="54"/>
     </row>
     <row r="38" spans="9:21" x14ac:dyDescent="0.25">
       <c r="I38" s="2" t="s">
@@ -3358,14 +3839,14 @@
         <v>380.97</v>
       </c>
       <c r="L38" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>-127.79000000000002</v>
       </c>
-      <c r="M38" s="36">
-        <f t="shared" si="7"/>
+      <c r="M38" s="53">
+        <f t="shared" si="11"/>
         <v>-0.33543323621282517</v>
       </c>
-      <c r="N38" s="36"/>
+      <c r="N38" s="53"/>
     </row>
     <row r="39" spans="9:21" x14ac:dyDescent="0.25">
       <c r="I39" s="6" t="s">
@@ -3378,14 +3859,14 @@
         <v>16.91</v>
       </c>
       <c r="L39" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>-9.7100000000000009</v>
       </c>
-      <c r="M39" s="37">
-        <f t="shared" si="7"/>
+      <c r="M39" s="54">
+        <f t="shared" si="11"/>
         <v>-0.57421643997634542</v>
       </c>
-      <c r="N39" s="37"/>
+      <c r="N39" s="54"/>
     </row>
     <row r="40" spans="9:21" x14ac:dyDescent="0.25">
       <c r="I40" s="2" t="s">
@@ -3398,14 +3879,14 @@
         <v>2.02</v>
       </c>
       <c r="L40" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>6.999999999999984E-2</v>
       </c>
-      <c r="M40" s="36">
-        <f t="shared" si="7"/>
+      <c r="M40" s="53">
+        <f t="shared" si="11"/>
         <v>3.4653465346534573E-2</v>
       </c>
-      <c r="N40" s="36"/>
+      <c r="N40" s="53"/>
     </row>
     <row r="41" spans="9:21" x14ac:dyDescent="0.25">
       <c r="I41" s="12" t="s">
@@ -3420,14 +3901,14 @@
         <v>408.66</v>
       </c>
       <c r="L41" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>-117.79000000000008</v>
       </c>
-      <c r="M41" s="37">
-        <f t="shared" si="7"/>
+      <c r="M41" s="54">
+        <f t="shared" si="11"/>
         <v>-0.28823471834777092</v>
       </c>
-      <c r="N41" s="37"/>
+      <c r="N41" s="54"/>
     </row>
     <row r="42" spans="9:21" x14ac:dyDescent="0.25">
       <c r="I42" s="10" t="s">
@@ -3442,14 +3923,14 @@
         <v>486.17</v>
       </c>
       <c r="L42" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>-44.700000000000045</v>
       </c>
-      <c r="M42" s="36">
-        <f t="shared" si="7"/>
+      <c r="M42" s="53">
+        <f t="shared" si="11"/>
         <v>-9.1943147458707949E-2</v>
       </c>
-      <c r="N42" s="36"/>
+      <c r="N42" s="53"/>
     </row>
     <row r="43" spans="9:21" x14ac:dyDescent="0.25">
       <c r="I43" s="12" t="s">
@@ -3464,398 +3945,26 @@
         <v>3815.090000000002</v>
       </c>
       <c r="L43" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>518.85999999999785</v>
       </c>
-      <c r="M43" s="37">
-        <f t="shared" si="7"/>
+      <c r="M43" s="54">
+        <f t="shared" si="11"/>
         <v>0.13600203402803016</v>
       </c>
-      <c r="N43" s="37"/>
+      <c r="N43" s="54"/>
     </row>
     <row r="45" spans="9:21" x14ac:dyDescent="0.25">
       <c r="I45" s="13"/>
     </row>
-    <row r="49" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="40" t="s">
-        <v>131</v>
-      </c>
-      <c r="C49" s="40"/>
-      <c r="D49" s="40"/>
-      <c r="E49" s="40"/>
-    </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B50" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B51" s="38" t="s">
-        <v>134</v>
-      </c>
-      <c r="C51" s="38"/>
-      <c r="D51" s="38"/>
-      <c r="E51" s="38"/>
-    </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B52" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="C52" s="43">
-        <f>J21/J41</f>
-        <v>2.6108227043008907</v>
-      </c>
-      <c r="D52" s="43">
-        <f>K21/K41</f>
-        <v>1.4697792786179218</v>
-      </c>
-      <c r="E52" s="14" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B53" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="C53" s="44">
-        <f>(J21-J14)/J41</f>
-        <v>2.6107539450613682</v>
-      </c>
-      <c r="D53" s="44">
-        <f>(K21-K14)/K41</f>
-        <v>1.4697303381784368</v>
-      </c>
-      <c r="E53" s="48" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B54" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C54" s="43">
-        <f>J16/J41</f>
-        <v>1.3262969711554993</v>
-      </c>
-      <c r="D54" s="43">
-        <f>K16/K41</f>
-        <v>0.34556844320461994</v>
-      </c>
-      <c r="E54" s="14" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B55" s="38" t="s">
-        <v>140</v>
-      </c>
-      <c r="C55" s="38"/>
-      <c r="D55" s="38"/>
-      <c r="E55" s="38"/>
-    </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B56" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C56" s="16" t="s">
-        <v>142</v>
-      </c>
-      <c r="D56" s="16" t="s">
-        <v>142</v>
-      </c>
-      <c r="E56" s="14" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="57" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B57" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="C57" s="45">
-        <f>J42/J28</f>
-        <v>0.1134161254521539</v>
-      </c>
-      <c r="D57" s="45">
-        <f>K42/K28</f>
-        <v>0.14604436273626273</v>
-      </c>
-      <c r="E57" s="15" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="58" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B58" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C58" s="16" t="s">
-        <v>147</v>
-      </c>
-      <c r="D58" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="E58" s="14" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="59" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B59" s="38" t="s">
-        <v>149</v>
-      </c>
-      <c r="C59" s="38"/>
-      <c r="D59" s="38"/>
-      <c r="E59" s="38"/>
-    </row>
-    <row r="60" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B60" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C60" s="46">
-        <f>(C6-C9)/C6</f>
-        <v>0.25580787879777317</v>
-      </c>
-      <c r="D60" s="46">
-        <f>(D6-D9)/D6</f>
-        <v>0.32467290255939396</v>
-      </c>
-      <c r="E60" s="14" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="61" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B61" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="C61" s="47">
-        <f>(C16+C12+C11)/C6</f>
-        <v>2.5141625716291308E-2</v>
-      </c>
-      <c r="D61" s="47">
-        <f>(D16+D12+D11)/D6</f>
-        <v>0.13264661999311361</v>
-      </c>
-      <c r="E61" s="15" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="62" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B62" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C62" s="46">
-        <f>C18/C6</f>
-        <v>-0.42022431554372863</v>
-      </c>
-      <c r="D62" s="46">
-        <f>D18/D6</f>
-        <v>-0.53062951910937695</v>
-      </c>
-      <c r="E62" s="14" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="63" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B63" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="C63" s="47">
-        <f>C18/J28</f>
-        <v>-6.6127507398881971E-2</v>
-      </c>
-      <c r="D63" s="47">
-        <f>D18/K28</f>
-        <v>-0.11110810713384518</v>
-      </c>
-      <c r="E63" s="15" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="64" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B64" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C64" s="46">
-        <f>(C16+C11)/(J28+J33)</f>
-        <v>-6.0419284308002842E-2</v>
-      </c>
-      <c r="D64" s="46">
-        <f>(D16+D11)/(K28+K33)</f>
-        <v>-0.10658666110855056</v>
-      </c>
-      <c r="E64" s="14" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="65" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B65" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="C65" s="45">
-        <f>C18/J22</f>
-        <v>-5.9393192626383616E-2</v>
-      </c>
-      <c r="D65" s="45">
-        <f>D18/K22</f>
-        <v>-9.6952269611556618E-2</v>
-      </c>
-      <c r="E65" s="15" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="66" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B66" s="38" t="s">
-        <v>159</v>
-      </c>
-      <c r="C66" s="38"/>
-      <c r="D66" s="38"/>
-      <c r="E66" s="38"/>
-    </row>
-    <row r="67" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B67" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="C67" s="44">
-        <f>C4/((K15+J15)/2)</f>
-        <v>1.9378604333731444</v>
-      </c>
-      <c r="D67" s="44">
-        <f>D4/((L15+K15)/2)</f>
-        <v>5.0683027794204607</v>
-      </c>
-      <c r="E67" s="15" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="68" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B68" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="C68" s="49">
-        <f>365/C67</f>
-        <v>188.352057616792</v>
-      </c>
-      <c r="D68" s="49">
-        <f>365/D67</f>
-        <v>72.016218423662565</v>
-      </c>
-      <c r="E68" s="14" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="69" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B69" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="C69" s="44">
-        <f>C4/(J21-J41)</f>
-        <v>1.2120416613309428</v>
-      </c>
-      <c r="D69" s="44">
-        <f>D4/(K21-K41)</f>
-        <v>3.5714136889259303</v>
-      </c>
-      <c r="E69" s="15" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="70" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B70" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="C70" s="43">
-        <f>C4/J22</f>
-        <v>0.13103651966043892</v>
-      </c>
-      <c r="D70" s="43">
-        <f>D4/K22</f>
-        <v>0.17972356270167264</v>
-      </c>
-      <c r="E70" s="14" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="71" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B71" s="38" t="s">
-        <v>168</v>
-      </c>
-      <c r="C71" s="38"/>
-      <c r="D71" s="38"/>
-      <c r="E71" s="38"/>
-    </row>
-    <row r="72" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B72" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C72" s="26">
-        <v>19017.05</v>
-      </c>
-      <c r="D72" s="26">
-        <v>18759.61</v>
-      </c>
-      <c r="E72" s="14" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="73" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B73" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="C73" s="25">
-        <f>J28</f>
-        <v>3892.4799999999996</v>
-      </c>
-      <c r="D73" s="25">
-        <f>K28</f>
-        <v>3328.9200000000019</v>
-      </c>
-      <c r="E73" s="15" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="74" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B74" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="C74" s="26">
-        <v>821</v>
-      </c>
-      <c r="D74" s="26">
-        <v>546</v>
-      </c>
-      <c r="E74" s="14" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="75" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B75" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="C75" s="25">
-        <v>2.2799999999999998</v>
-      </c>
-      <c r="D75" s="25">
-        <v>82.99</v>
-      </c>
-      <c r="E75" s="15" t="s">
-        <v>176</v>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="100">
-    <mergeCell ref="B71:E71"/>
-    <mergeCell ref="B49:E49"/>
-    <mergeCell ref="B51:E51"/>
-    <mergeCell ref="B55:E55"/>
-    <mergeCell ref="B59:E59"/>
-    <mergeCell ref="B66:E66"/>
+    <mergeCell ref="W23:Z23"/>
+    <mergeCell ref="W1:Z1"/>
+    <mergeCell ref="W3:Z3"/>
+    <mergeCell ref="W7:Z7"/>
+    <mergeCell ref="W11:Z11"/>
+    <mergeCell ref="W18:Z18"/>
     <mergeCell ref="T36:U36"/>
     <mergeCell ref="T27:U27"/>
     <mergeCell ref="P29:U29"/>
@@ -3958,413 +4067,403 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:C59"/>
+  <dimension ref="B1:C58"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="43.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.140625" customWidth="1"/>
     <col min="3" max="3" width="58.5703125" customWidth="1"/>
     <col min="4" max="4" width="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="40" t="s">
+      <c r="B1" s="57" t="s">
+        <v>176</v>
+      </c>
+      <c r="C1" s="57"/>
+    </row>
+    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B2" s="13"/>
+    </row>
+    <row r="4" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="59" t="s">
         <v>177</v>
       </c>
-      <c r="C1" s="40"/>
-    </row>
-    <row r="2" spans="2:3" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="13" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="4" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="42" t="s">
-        <v>179</v>
-      </c>
-      <c r="C4" s="42"/>
+      <c r="C4" s="59"/>
     </row>
     <row r="5" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="17" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="18" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="18" t="s">
-        <v>184</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>185</v>
+        <v>182</v>
+      </c>
+      <c r="C7" s="43" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="18" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="18" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="18" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="11" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="18" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="13" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="42" t="s">
-        <v>194</v>
-      </c>
-      <c r="C13" s="42"/>
+      <c r="B13" s="59" t="s">
+        <v>191</v>
+      </c>
+      <c r="C13" s="59"/>
     </row>
     <row r="14" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="17" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="15" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="20" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="16" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="20" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="20" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C17" s="21" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="20" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="19" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="20" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="20" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C20" s="21" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="22" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="42" t="s">
-        <v>209</v>
-      </c>
-      <c r="C22" s="42"/>
+      <c r="B22" s="59" t="s">
+        <v>206</v>
+      </c>
+      <c r="C22" s="59"/>
     </row>
     <row r="23" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="17" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="24" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="18" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C24" s="20" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="25" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="18" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="26" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="18" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C26" s="20" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="27" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="18" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="28" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="18" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C28" s="20" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="30" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="42" t="s">
-        <v>222</v>
-      </c>
-      <c r="C30" s="42"/>
+      <c r="B30" s="59" t="s">
+        <v>219</v>
+      </c>
+      <c r="C30" s="59"/>
     </row>
     <row r="31" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="17" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="32" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="22" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C32" s="23" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
     </row>
     <row r="33" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="22" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C33" s="23" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="34" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="22" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C34" s="23" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
     </row>
     <row r="35" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="22" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C35" s="23" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="36" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="22" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C36" s="23" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="37" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="22" t="s">
+        <v>232</v>
+      </c>
+      <c r="C37" s="23" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="39" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="59" t="s">
+        <v>234</v>
+      </c>
+      <c r="C39" s="59"/>
+    </row>
+    <row r="40" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="17" t="s">
         <v>235</v>
       </c>
-      <c r="C37" s="23" t="s">
+      <c r="C40" s="17" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="38" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="22" t="s">
+    <row r="41" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="24" t="s">
         <v>237</v>
       </c>
-      <c r="C38" s="23" t="s">
+      <c r="C41" s="23" t="s">
         <v>238</v>
-      </c>
-    </row>
-    <row r="40" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="42" t="s">
-        <v>239</v>
-      </c>
-      <c r="C40" s="42"/>
-    </row>
-    <row r="41" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="17" t="s">
-        <v>240</v>
-      </c>
-      <c r="C41" s="17" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="42" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="24" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C42" s="23" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="43" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="24" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C43" s="23" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
     <row r="44" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="24" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C44" s="23" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="45" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="24" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="C45" s="23" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="46" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="24" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C46" s="23" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="47" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="24" t="s">
+        <v>249</v>
+      </c>
+      <c r="C47" s="23" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="49" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="59" t="s">
+        <v>251</v>
+      </c>
+      <c r="C49" s="59"/>
+    </row>
+    <row r="50" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B50" s="17" t="s">
         <v>252</v>
       </c>
-      <c r="C47" s="23" t="s">
+      <c r="C50" s="17" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="48" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="24" t="s">
+    <row r="51" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B51" s="19" t="s">
         <v>254</v>
       </c>
-      <c r="C48" s="23" t="s">
+      <c r="C51" s="23" t="s">
         <v>255</v>
-      </c>
-    </row>
-    <row r="50" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="42" t="s">
-        <v>256</v>
-      </c>
-      <c r="C50" s="42"/>
-    </row>
-    <row r="51" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="17" t="s">
-        <v>257</v>
-      </c>
-      <c r="C51" s="17" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="52" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B52" s="19" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C52" s="23" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="53" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="19" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C53" s="23" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
     </row>
     <row r="54" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="19" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C54" s="23" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
     </row>
     <row r="55" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="19" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C55" s="23" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="56" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="19" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C56" s="23" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="57" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="19" t="s">
-        <v>269</v>
-      </c>
-      <c r="C57" s="23" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="59" spans="2:3" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="13"/>
+        <v>265</v>
+      </c>
+    </row>
+    <row r="58" spans="2:3" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B58" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B49:C49"/>
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B13:C13"/>

--- a/myprojects/FHEL/FHEL_Financial_Health_Analysis.xlsx
+++ b/myprojects/FHEL/FHEL_Financial_Health_Analysis.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Documents\GitHub\inakm.github.io\myprojects\FHEL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\inanj\Documents\GitHub\inakm.github.io\myprojects\FHEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1175BE19-33A9-437B-8D95-86D3228BD752}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1350" windowWidth="28800" windowHeight="13260" tabRatio="500" activeTab="2"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HOME" sheetId="1" r:id="rId1"/>
     <sheet name="Health Analysis" sheetId="2" r:id="rId2"/>
     <sheet name="Business Analysis" sheetId="6" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="152511" iterateDelta="1E-4"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -25,6 +26,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -871,7 +874,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%;\(0.0%\);\-"/>
   </numFmts>
@@ -1185,7 +1188,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1259,12 +1262,6 @@
     <xf numFmtId="0" fontId="12" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="13" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1290,7 +1287,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
@@ -1298,10 +1294,17 @@
     <xf numFmtId="0" fontId="17" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1310,34 +1313,27 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1622,326 +1618,325 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:H27"/>
-  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="3" width="28" customWidth="1"/>
-    <col min="4" max="4" width="36.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" customWidth="1"/>
-    <col min="7" max="7" width="5.7109375" customWidth="1"/>
-    <col min="8" max="8" width="6.5703125" customWidth="1"/>
+    <col min="6" max="6" width="9.109375" customWidth="1"/>
+    <col min="7" max="7" width="5.6640625" customWidth="1"/>
+    <col min="8" max="8" width="6.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="50" t="s">
+    <row r="2" spans="2:8" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-    </row>
-    <row r="3" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="51" t="s">
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
+    </row>
+    <row r="3" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-    </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="47" t="s">
+      <c r="C3" s="44"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="44"/>
+      <c r="G3" s="44"/>
+      <c r="H3" s="44"/>
+    </row>
+    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="47"/>
-      <c r="D5" s="48" t="s">
+      <c r="C5" s="45"/>
+      <c r="D5" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="48"/>
-      <c r="H5" s="48"/>
-    </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="47" t="s">
+      <c r="E5" s="46"/>
+      <c r="F5" s="46"/>
+      <c r="G5" s="46"/>
+      <c r="H5" s="46"/>
+    </row>
+    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="47"/>
-      <c r="D6" s="48" t="s">
+      <c r="C6" s="45"/>
+      <c r="D6" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="48"/>
-      <c r="F6" s="48"/>
-      <c r="G6" s="48"/>
-      <c r="H6" s="48"/>
-    </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="47" t="s">
+      <c r="E6" s="46"/>
+      <c r="F6" s="46"/>
+      <c r="G6" s="46"/>
+      <c r="H6" s="46"/>
+    </row>
+    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="47"/>
-      <c r="D7" s="48" t="s">
+      <c r="C7" s="45"/>
+      <c r="D7" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="48"/>
-      <c r="F7" s="48"/>
-      <c r="G7" s="48"/>
-      <c r="H7" s="48"/>
-    </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="47" t="s">
+      <c r="E7" s="46"/>
+      <c r="F7" s="46"/>
+      <c r="G7" s="46"/>
+      <c r="H7" s="46"/>
+    </row>
+    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="47"/>
-      <c r="D8" s="48" t="s">
+      <c r="C8" s="45"/>
+      <c r="D8" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="48"/>
-      <c r="F8" s="48"/>
-      <c r="G8" s="48"/>
-      <c r="H8" s="48"/>
-    </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="47" t="s">
+      <c r="E8" s="46"/>
+      <c r="F8" s="46"/>
+      <c r="G8" s="46"/>
+      <c r="H8" s="46"/>
+    </row>
+    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="47"/>
-      <c r="D9" s="48" t="s">
+      <c r="C9" s="45"/>
+      <c r="D9" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="48"/>
-      <c r="F9" s="48"/>
-      <c r="G9" s="48"/>
-      <c r="H9" s="48"/>
-    </row>
-    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="47" t="s">
+      <c r="E9" s="46"/>
+      <c r="F9" s="46"/>
+      <c r="G9" s="46"/>
+      <c r="H9" s="46"/>
+    </row>
+    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="47"/>
-      <c r="D10" s="48" t="s">
+      <c r="C10" s="45"/>
+      <c r="D10" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="E10" s="48"/>
-      <c r="F10" s="48"/>
-      <c r="G10" s="48"/>
-      <c r="H10" s="48"/>
-    </row>
-    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="47" t="s">
+      <c r="E10" s="46"/>
+      <c r="F10" s="46"/>
+      <c r="G10" s="46"/>
+      <c r="H10" s="46"/>
+    </row>
+    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="47"/>
-      <c r="D11" s="48" t="s">
+      <c r="C11" s="45"/>
+      <c r="D11" s="46" t="s">
         <v>267</v>
       </c>
-      <c r="E11" s="48"/>
-      <c r="F11" s="48"/>
-      <c r="G11" s="48"/>
-      <c r="H11" s="48"/>
-    </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="47" t="s">
+      <c r="E11" s="46"/>
+      <c r="F11" s="46"/>
+      <c r="G11" s="46"/>
+      <c r="H11" s="46"/>
+    </row>
+    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="47"/>
-      <c r="D12" s="48" t="s">
+      <c r="C12" s="45"/>
+      <c r="D12" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="E12" s="48"/>
-      <c r="F12" s="48"/>
-      <c r="G12" s="48"/>
-      <c r="H12" s="48"/>
-    </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="47" t="s">
+      <c r="E12" s="46"/>
+      <c r="F12" s="46"/>
+      <c r="G12" s="46"/>
+      <c r="H12" s="46"/>
+    </row>
+    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="47"/>
-      <c r="D13" s="48" t="s">
+      <c r="C13" s="45"/>
+      <c r="D13" s="46" t="s">
         <v>266</v>
       </c>
-      <c r="E13" s="48"/>
-      <c r="F13" s="48"/>
-      <c r="G13" s="48"/>
-      <c r="H13" s="48"/>
-    </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="47" t="s">
+      <c r="E13" s="46"/>
+      <c r="F13" s="46"/>
+      <c r="G13" s="46"/>
+      <c r="H13" s="46"/>
+    </row>
+    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="47"/>
-      <c r="D14" s="48" t="s">
+      <c r="C14" s="45"/>
+      <c r="D14" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="48"/>
-      <c r="F14" s="48"/>
-      <c r="G14" s="48"/>
-      <c r="H14" s="48"/>
-    </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="49" t="s">
+      <c r="E14" s="46"/>
+      <c r="F14" s="46"/>
+      <c r="G14" s="46"/>
+      <c r="H14" s="46"/>
+    </row>
+    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="49"/>
-      <c r="D16" s="49"/>
-      <c r="E16" s="49"/>
-      <c r="F16" s="49"/>
-      <c r="G16" s="49"/>
-      <c r="H16" s="49"/>
-    </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="46" t="s">
+      <c r="C16" s="47"/>
+      <c r="D16" s="47"/>
+      <c r="E16" s="47"/>
+      <c r="F16" s="47"/>
+      <c r="G16" s="47"/>
+      <c r="H16" s="47"/>
+    </row>
+    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="48" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="46"/>
-      <c r="D18" s="46"/>
-      <c r="E18" s="46"/>
-      <c r="F18" s="46"/>
-      <c r="G18" s="46"/>
-      <c r="H18" s="46"/>
-    </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="44" t="s">
+      <c r="C18" s="48"/>
+      <c r="D18" s="48"/>
+      <c r="E18" s="48"/>
+      <c r="F18" s="48"/>
+      <c r="G18" s="48"/>
+      <c r="H18" s="48"/>
+    </row>
+    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="49" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="44"/>
-      <c r="D19" s="45" t="s">
+      <c r="C19" s="49"/>
+      <c r="D19" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="E19" s="45"/>
-      <c r="F19" s="45"/>
-      <c r="G19" s="45"/>
-      <c r="H19" s="45"/>
-    </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="44" t="s">
+      <c r="E19" s="50"/>
+      <c r="F19" s="50"/>
+      <c r="G19" s="50"/>
+      <c r="H19" s="50"/>
+    </row>
+    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="49" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="44"/>
-      <c r="D20" s="45" t="s">
+      <c r="C20" s="49"/>
+      <c r="D20" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="E20" s="45"/>
-      <c r="F20" s="45"/>
-      <c r="G20" s="45"/>
-      <c r="H20" s="45"/>
-    </row>
-    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="44" t="s">
+      <c r="E20" s="50"/>
+      <c r="F20" s="50"/>
+      <c r="G20" s="50"/>
+      <c r="H20" s="50"/>
+    </row>
+    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="C21" s="44"/>
-      <c r="D21" s="45" t="s">
+      <c r="C21" s="49"/>
+      <c r="D21" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="E21" s="45"/>
-      <c r="F21" s="45"/>
-      <c r="G21" s="45"/>
-      <c r="H21" s="45"/>
-    </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="44" t="s">
+      <c r="E21" s="50"/>
+      <c r="F21" s="50"/>
+      <c r="G21" s="50"/>
+      <c r="H21" s="50"/>
+    </row>
+    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="49" t="s">
         <v>28</v>
       </c>
-      <c r="C22" s="44"/>
-      <c r="D22" s="45" t="s">
+      <c r="C22" s="49"/>
+      <c r="D22" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="E22" s="45"/>
-      <c r="F22" s="45"/>
-      <c r="G22" s="45"/>
-      <c r="H22" s="45"/>
-    </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="44" t="s">
+      <c r="E22" s="50"/>
+      <c r="F22" s="50"/>
+      <c r="G22" s="50"/>
+      <c r="H22" s="50"/>
+    </row>
+    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="44"/>
-      <c r="D23" s="45" t="s">
+      <c r="C23" s="49"/>
+      <c r="D23" s="50" t="s">
         <v>31</v>
       </c>
-      <c r="E23" s="45"/>
-      <c r="F23" s="45"/>
-      <c r="G23" s="45"/>
-      <c r="H23" s="45"/>
-    </row>
-    <row r="24" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="34" t="s">
+      <c r="E23" s="50"/>
+      <c r="F23" s="50"/>
+      <c r="G23" s="50"/>
+      <c r="H23" s="50"/>
+    </row>
+    <row r="24" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B25" s="32" t="s">
         <v>276</v>
       </c>
-      <c r="C25" s="35"/>
-      <c r="D25" s="36" t="s">
+      <c r="C25" s="33"/>
+      <c r="D25" s="34" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="37" t="s">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B26" s="35" t="s">
         <v>273</v>
       </c>
-      <c r="C26" s="38"/>
-      <c r="D26" s="39" t="s">
+      <c r="D26" s="36" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="40" t="s">
+    <row r="27" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B27" s="37" t="s">
         <v>272</v>
       </c>
-      <c r="C27" s="41"/>
-      <c r="D27" s="42" t="s">
+      <c r="C27" s="38"/>
+      <c r="D27" s="39" t="s">
         <v>271</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="34">
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:H21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:H22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:H23"/>
+    <mergeCell ref="B18:H18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:H19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:H20"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:H13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:H14"/>
+    <mergeCell ref="B16:H16"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:H10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:H8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:H9"/>
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="D5:H5"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="D6:H6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D7:H7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:H8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:H9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:H10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:H11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:H12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:H13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:H14"/>
-    <mergeCell ref="B16:H16"/>
-    <mergeCell ref="B18:H18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:H19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:H20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:H21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:H22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:H23"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="D26" r:id="rId1"/>
-    <hyperlink ref="D27" r:id="rId2"/>
+    <hyperlink ref="D26" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="D27" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId3"/>
@@ -1949,64 +1944,64 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B1:Z45"/>
-  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="30.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="20" customWidth="1"/>
-    <col min="5" max="5" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.28515625" customWidth="1"/>
-    <col min="8" max="8" width="1.85546875" customWidth="1"/>
-    <col min="9" max="9" width="33.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="2.140625" customWidth="1"/>
-    <col min="16" max="16" width="36.140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.33203125" customWidth="1"/>
+    <col min="8" max="8" width="1.88671875" customWidth="1"/>
+    <col min="9" max="9" width="33.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="2.109375" customWidth="1"/>
+    <col min="16" max="16" width="36.109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.109375" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="2" customWidth="1"/>
-    <col min="23" max="23" width="30.5703125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="39.85546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="30.5546875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="39.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="57" t="s">
+    <row r="1" spans="2:26" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="42" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="I1" s="57" t="s">
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="I1" s="42" t="s">
         <v>61</v>
       </c>
-      <c r="J1" s="57"/>
-      <c r="K1" s="57"/>
-      <c r="L1" s="57"/>
-      <c r="M1" s="57"/>
-      <c r="N1" s="57"/>
-      <c r="P1" s="57" t="s">
+      <c r="J1" s="42"/>
+      <c r="K1" s="42"/>
+      <c r="L1" s="42"/>
+      <c r="M1" s="42"/>
+      <c r="N1" s="42"/>
+      <c r="P1" s="42" t="s">
         <v>99</v>
       </c>
-      <c r="Q1" s="57"/>
-      <c r="R1" s="57"/>
-      <c r="S1" s="57"/>
-      <c r="T1" s="57"/>
-      <c r="U1" s="57"/>
-      <c r="W1" s="57" t="s">
+      <c r="Q1" s="42"/>
+      <c r="R1" s="42"/>
+      <c r="S1" s="42"/>
+      <c r="T1" s="42"/>
+      <c r="U1" s="42"/>
+      <c r="W1" s="42" t="s">
         <v>275</v>
       </c>
-      <c r="X1" s="57"/>
-      <c r="Y1" s="57"/>
-      <c r="Z1" s="57"/>
-    </row>
-    <row r="2" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="X1" s="42"/>
+      <c r="Y1" s="42"/>
+      <c r="Z1" s="42"/>
+    </row>
+    <row r="2" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>33</v>
       </c>
@@ -2019,10 +2014,10 @@
       <c r="E2" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F2" s="56" t="s">
+      <c r="F2" s="54" t="s">
         <v>37</v>
       </c>
-      <c r="G2" s="56"/>
+      <c r="G2" s="54"/>
       <c r="I2" s="1" t="s">
         <v>33</v>
       </c>
@@ -2035,10 +2030,10 @@
       <c r="L2" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="M2" s="56" t="s">
+      <c r="M2" s="54" t="s">
         <v>37</v>
       </c>
-      <c r="N2" s="56"/>
+      <c r="N2" s="54"/>
       <c r="P2" s="1" t="s">
         <v>33</v>
       </c>
@@ -2051,10 +2046,10 @@
       <c r="S2" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="T2" s="56" t="s">
+      <c r="T2" s="54" t="s">
         <v>37</v>
       </c>
-      <c r="U2" s="56"/>
+      <c r="U2" s="54"/>
       <c r="W2" s="1" t="s">
         <v>131</v>
       </c>
@@ -2068,39 +2063,39 @@
         <v>132</v>
       </c>
     </row>
-    <row r="3" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="55" t="s">
+    <row r="3" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="51" t="s">
         <v>38</v>
       </c>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
-      <c r="I3" s="55" t="s">
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="I3" s="51" t="s">
         <v>62</v>
       </c>
-      <c r="J3" s="55"/>
-      <c r="K3" s="55"/>
-      <c r="L3" s="55"/>
-      <c r="M3" s="55"/>
-      <c r="N3" s="55"/>
-      <c r="P3" s="55" t="s">
+      <c r="J3" s="51"/>
+      <c r="K3" s="51"/>
+      <c r="L3" s="51"/>
+      <c r="M3" s="51"/>
+      <c r="N3" s="51"/>
+      <c r="P3" s="51" t="s">
         <v>100</v>
       </c>
-      <c r="Q3" s="55"/>
-      <c r="R3" s="55"/>
-      <c r="S3" s="55"/>
-      <c r="T3" s="55"/>
-      <c r="U3" s="55"/>
-      <c r="W3" s="55" t="s">
+      <c r="Q3" s="51"/>
+      <c r="R3" s="51"/>
+      <c r="S3" s="51"/>
+      <c r="T3" s="51"/>
+      <c r="U3" s="51"/>
+      <c r="W3" s="51" t="s">
         <v>133</v>
       </c>
-      <c r="X3" s="55"/>
-      <c r="Y3" s="55"/>
-      <c r="Z3" s="55"/>
-    </row>
-    <row r="4" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="X3" s="51"/>
+      <c r="Y3" s="51"/>
+      <c r="Z3" s="51"/>
+    </row>
+    <row r="4" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
         <v>39</v>
       </c>
@@ -2114,19 +2109,19 @@
         <f>C4-D4</f>
         <v>-117.75</v>
       </c>
-      <c r="F4" s="53">
+      <c r="F4" s="52">
         <f>(C4-D4)/ABS(D4)</f>
         <v>-0.17173735488011202</v>
       </c>
-      <c r="G4" s="53"/>
-      <c r="I4" s="58" t="s">
+      <c r="G4" s="52"/>
+      <c r="I4" s="55" t="s">
         <v>63</v>
       </c>
-      <c r="J4" s="58"/>
-      <c r="K4" s="58"/>
-      <c r="L4" s="58"/>
-      <c r="M4" s="58"/>
-      <c r="N4" s="58"/>
+      <c r="J4" s="55"/>
+      <c r="K4" s="55"/>
+      <c r="L4" s="55"/>
+      <c r="M4" s="55"/>
+      <c r="N4" s="55"/>
       <c r="P4" s="2" t="s">
         <v>101</v>
       </c>
@@ -2140,19 +2135,19 @@
         <f t="shared" ref="S4:S19" si="0">Q4-R4</f>
         <v>115.15000000000003</v>
       </c>
-      <c r="T4" s="53">
+      <c r="T4" s="52">
         <f t="shared" ref="T4:T19" si="1">(Q4-R4)/ABS(R4)</f>
         <v>0.30908602872097712</v>
       </c>
-      <c r="U4" s="53"/>
+      <c r="U4" s="52"/>
       <c r="W4" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="X4" s="27">
+      <c r="X4" s="25">
         <f>J21/J41</f>
         <v>2.6108227043008907</v>
       </c>
-      <c r="Y4" s="27">
+      <c r="Y4" s="25">
         <f>K21/K41</f>
         <v>1.4697792786179218</v>
       </c>
@@ -2160,7 +2155,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="5" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="6" t="s">
         <v>40</v>
       </c>
@@ -2174,11 +2169,11 @@
         <f>C5-D5</f>
         <v>33.24</v>
       </c>
-      <c r="F5" s="54">
+      <c r="F5" s="53">
         <f>(C5-D5)/ABS(D5)</f>
         <v>2.9157894736842107</v>
       </c>
-      <c r="G5" s="54"/>
+      <c r="G5" s="53"/>
       <c r="I5" s="6" t="s">
         <v>64</v>
       </c>
@@ -2192,11 +2187,11 @@
         <f t="shared" ref="L5:L11" si="2">J5-K5</f>
         <v>53.960000000000036</v>
       </c>
-      <c r="M5" s="54">
+      <c r="M5" s="53">
         <f t="shared" ref="M5:M11" si="3">(J5-K5)/ABS(K5)</f>
         <v>2.1674425704037256E-2</v>
       </c>
-      <c r="N5" s="54"/>
+      <c r="N5" s="53"/>
       <c r="P5" s="6" t="s">
         <v>102</v>
       </c>
@@ -2210,27 +2205,27 @@
         <f t="shared" si="0"/>
         <v>-195.86</v>
       </c>
-      <c r="T5" s="54">
+      <c r="T5" s="53">
         <f t="shared" si="1"/>
         <v>-0.4299512666286166</v>
       </c>
-      <c r="U5" s="54"/>
+      <c r="U5" s="53"/>
       <c r="W5" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="X5" s="28">
+      <c r="X5" s="26">
         <f>(J21-J14)/J41</f>
         <v>2.6107539450613682</v>
       </c>
-      <c r="Y5" s="28">
+      <c r="Y5" s="26">
         <f>(K21-K14)/K41</f>
         <v>1.4697303381784368</v>
       </c>
-      <c r="Z5" s="32" t="s">
+      <c r="Z5" s="30" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="6" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="10" t="s">
         <v>41</v>
       </c>
@@ -2246,11 +2241,11 @@
         <f>C6-D6</f>
         <v>-84.509999999999991</v>
       </c>
-      <c r="F6" s="53">
+      <c r="F6" s="52">
         <f>(C6-D6)/ABS(D6)</f>
         <v>-0.12124124870882588</v>
       </c>
-      <c r="G6" s="53"/>
+      <c r="G6" s="52"/>
       <c r="I6" s="2" t="s">
         <v>65</v>
       </c>
@@ -2264,11 +2259,11 @@
         <f t="shared" si="2"/>
         <v>-0.22999999999999998</v>
       </c>
-      <c r="M6" s="53">
+      <c r="M6" s="52">
         <f t="shared" si="3"/>
         <v>-0.31506849315068491</v>
       </c>
-      <c r="N6" s="53"/>
+      <c r="N6" s="52"/>
       <c r="P6" s="2" t="s">
         <v>103</v>
       </c>
@@ -2282,19 +2277,19 @@
         <f t="shared" si="0"/>
         <v>-5.15</v>
       </c>
-      <c r="T6" s="53">
+      <c r="T6" s="52">
         <f t="shared" si="1"/>
         <v>-0.71727019498607247</v>
       </c>
-      <c r="U6" s="53"/>
+      <c r="U6" s="52"/>
       <c r="W6" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="X6" s="27">
+      <c r="X6" s="25">
         <f>J16/J41</f>
         <v>1.3262969711554993</v>
       </c>
-      <c r="Y6" s="27">
+      <c r="Y6" s="25">
         <f>K16/K41</f>
         <v>0.34556844320461994</v>
       </c>
@@ -2302,7 +2297,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="7" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:26" x14ac:dyDescent="0.3">
       <c r="I7" s="6" t="s">
         <v>66</v>
       </c>
@@ -2316,11 +2311,11 @@
         <f t="shared" si="2"/>
         <v>306.64999999999998</v>
       </c>
-      <c r="M7" s="54">
+      <c r="M7" s="53">
         <f t="shared" si="3"/>
         <v>0.46891964217447812</v>
       </c>
-      <c r="N7" s="54"/>
+      <c r="N7" s="53"/>
       <c r="P7" s="6" t="s">
         <v>104</v>
       </c>
@@ -2334,27 +2329,27 @@
         <f t="shared" si="0"/>
         <v>-26.11</v>
       </c>
-      <c r="T7" s="54">
+      <c r="T7" s="53">
         <f t="shared" si="1"/>
         <v>-17.406666666666666</v>
       </c>
-      <c r="U7" s="54"/>
-      <c r="W7" s="55" t="s">
+      <c r="U7" s="53"/>
+      <c r="W7" s="51" t="s">
         <v>139</v>
       </c>
-      <c r="X7" s="55"/>
-      <c r="Y7" s="55"/>
-      <c r="Z7" s="55"/>
-    </row>
-    <row r="8" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="55" t="s">
+      <c r="X7" s="51"/>
+      <c r="Y7" s="51"/>
+      <c r="Z7" s="51"/>
+    </row>
+    <row r="8" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="C8" s="55"/>
-      <c r="D8" s="55"/>
-      <c r="E8" s="55"/>
-      <c r="F8" s="55"/>
-      <c r="G8" s="55"/>
+      <c r="C8" s="51"/>
+      <c r="D8" s="51"/>
+      <c r="E8" s="51"/>
+      <c r="F8" s="51"/>
+      <c r="G8" s="51"/>
       <c r="I8" s="2" t="s">
         <v>67</v>
       </c>
@@ -2368,11 +2363,11 @@
         <f t="shared" si="2"/>
         <v>-0.12000000000000001</v>
       </c>
-      <c r="M8" s="53">
+      <c r="M8" s="52">
         <f t="shared" si="3"/>
         <v>-0.92307692307692313</v>
       </c>
-      <c r="N8" s="53"/>
+      <c r="N8" s="52"/>
       <c r="P8" s="2" t="s">
         <v>105</v>
       </c>
@@ -2386,11 +2381,11 @@
         <f t="shared" si="0"/>
         <v>6.3299999999999992</v>
       </c>
-      <c r="T8" s="53">
+      <c r="T8" s="52">
         <f t="shared" si="1"/>
         <v>0.93225331369661257</v>
       </c>
-      <c r="U8" s="53"/>
+      <c r="U8" s="52"/>
       <c r="W8" s="2" t="s">
         <v>140</v>
       </c>
@@ -2404,7 +2399,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="9" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="6" t="s">
         <v>43</v>
       </c>
@@ -2418,11 +2413,11 @@
         <f t="shared" ref="E9:E14" si="4">C9-D9</f>
         <v>-14.890000000000043</v>
       </c>
-      <c r="F9" s="54">
+      <c r="F9" s="53">
         <f t="shared" ref="F9:F14" si="5">(C9-D9)/ABS(D9)</f>
         <v>-3.1631720944065689E-2</v>
       </c>
-      <c r="G9" s="54"/>
+      <c r="G9" s="53"/>
       <c r="I9" s="6" t="s">
         <v>68</v>
       </c>
@@ -2436,11 +2431,11 @@
         <f t="shared" si="2"/>
         <v>0.42000000000000171</v>
       </c>
-      <c r="M9" s="54">
+      <c r="M9" s="53">
         <f t="shared" si="3"/>
         <v>8.9609558352891343E-3</v>
       </c>
-      <c r="N9" s="54"/>
+      <c r="N9" s="53"/>
       <c r="P9" s="6" t="s">
         <v>106</v>
       </c>
@@ -2454,19 +2449,19 @@
         <f t="shared" si="0"/>
         <v>8.9999999999999969E-2</v>
       </c>
-      <c r="T9" s="54">
+      <c r="T9" s="53">
         <f t="shared" si="1"/>
         <v>0.10465116279069764</v>
       </c>
-      <c r="U9" s="54"/>
+      <c r="U9" s="53"/>
       <c r="W9" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="X9" s="29">
+      <c r="X9" s="27">
         <f>J42/J28</f>
         <v>0.1134161254521539</v>
       </c>
-      <c r="Y9" s="29">
+      <c r="Y9" s="27">
         <f>K42/K28</f>
         <v>0.14604436273626273</v>
       </c>
@@ -2474,7 +2469,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="10" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="2" t="s">
         <v>44</v>
       </c>
@@ -2488,11 +2483,11 @@
         <f t="shared" si="4"/>
         <v>13.919999999999998</v>
       </c>
-      <c r="F10" s="53">
+      <c r="F10" s="52">
         <f t="shared" si="5"/>
         <v>0.61429832303618703</v>
       </c>
-      <c r="G10" s="53"/>
+      <c r="G10" s="52"/>
       <c r="I10" s="2" t="s">
         <v>69</v>
       </c>
@@ -2506,11 +2501,11 @@
         <f>J10-K10</f>
         <v>-0.58999999999999986</v>
       </c>
-      <c r="M10" s="53">
+      <c r="M10" s="52">
         <f t="shared" si="3"/>
         <v>-2.5563258232235698E-2</v>
       </c>
-      <c r="N10" s="53"/>
+      <c r="N10" s="52"/>
       <c r="P10" s="10" t="s">
         <v>107</v>
       </c>
@@ -2526,11 +2521,11 @@
         <f t="shared" si="0"/>
         <v>-105.54999999999998</v>
       </c>
-      <c r="T10" s="53">
+      <c r="T10" s="52">
         <f t="shared" si="1"/>
         <v>-1.3154287138584244</v>
       </c>
-      <c r="U10" s="53"/>
+      <c r="U10" s="52"/>
       <c r="W10" s="2" t="s">
         <v>145</v>
       </c>
@@ -2544,7 +2539,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="11" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="6" t="s">
         <v>45</v>
       </c>
@@ -2558,11 +2553,11 @@
         <f t="shared" si="4"/>
         <v>6.3299999999999992</v>
       </c>
-      <c r="F11" s="54">
+      <c r="F11" s="53">
         <f t="shared" si="5"/>
         <v>0.93225331369661257</v>
       </c>
-      <c r="G11" s="54"/>
+      <c r="G11" s="53"/>
       <c r="I11" s="12" t="s">
         <v>70</v>
       </c>
@@ -2578,11 +2573,11 @@
         <f t="shared" si="2"/>
         <v>360.09000000000015</v>
       </c>
-      <c r="M11" s="54">
+      <c r="M11" s="53">
         <f t="shared" si="3"/>
         <v>0.11202645652437682</v>
       </c>
-      <c r="N11" s="54"/>
+      <c r="N11" s="53"/>
       <c r="P11" s="6" t="s">
         <v>108</v>
       </c>
@@ -2596,19 +2591,19 @@
         <f t="shared" si="0"/>
         <v>76.62</v>
       </c>
-      <c r="T11" s="54">
+      <c r="T11" s="53">
         <f t="shared" si="1"/>
         <v>2.4216182048040458</v>
       </c>
-      <c r="U11" s="54"/>
-      <c r="W11" s="55" t="s">
+      <c r="U11" s="53"/>
+      <c r="W11" s="51" t="s">
         <v>148</v>
       </c>
-      <c r="X11" s="55"/>
-      <c r="Y11" s="55"/>
-      <c r="Z11" s="55"/>
-    </row>
-    <row r="12" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="X11" s="51"/>
+      <c r="Y11" s="51"/>
+      <c r="Z11" s="51"/>
+    </row>
+    <row r="12" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="2" t="s">
         <v>46</v>
       </c>
@@ -2622,11 +2617,11 @@
         <f t="shared" si="4"/>
         <v>-195.86</v>
       </c>
-      <c r="F12" s="53">
+      <c r="F12" s="52">
         <f t="shared" si="5"/>
         <v>-0.4299512666286166</v>
       </c>
-      <c r="G12" s="53"/>
+      <c r="G12" s="52"/>
       <c r="P12" s="2" t="s">
         <v>109</v>
       </c>
@@ -2640,19 +2635,19 @@
         <f t="shared" si="0"/>
         <v>48.589999999999996</v>
       </c>
-      <c r="T12" s="53">
+      <c r="T12" s="52">
         <f t="shared" si="1"/>
         <v>3.2307180851063828</v>
       </c>
-      <c r="U12" s="53"/>
+      <c r="U12" s="52"/>
       <c r="W12" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="X12" s="30">
+      <c r="X12" s="28">
         <f>(C6-C9)/C6</f>
         <v>0.25580787879777317</v>
       </c>
-      <c r="Y12" s="30">
+      <c r="Y12" s="28">
         <f>(D6-D9)/D6</f>
         <v>0.32467290255939396</v>
       </c>
@@ -2660,7 +2655,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="13" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="6" t="s">
         <v>47</v>
       </c>
@@ -2674,19 +2669,19 @@
         <f t="shared" si="4"/>
         <v>-6.480000000000004</v>
       </c>
-      <c r="F13" s="54">
+      <c r="F13" s="53">
         <f t="shared" si="5"/>
         <v>-5.8278622178253477E-2</v>
       </c>
-      <c r="G13" s="54"/>
-      <c r="I13" s="58" t="s">
+      <c r="G13" s="53"/>
+      <c r="I13" s="55" t="s">
         <v>71</v>
       </c>
-      <c r="J13" s="58"/>
-      <c r="K13" s="58"/>
-      <c r="L13" s="58"/>
-      <c r="M13" s="58"/>
-      <c r="N13" s="58"/>
+      <c r="J13" s="55"/>
+      <c r="K13" s="55"/>
+      <c r="L13" s="55"/>
+      <c r="M13" s="55"/>
+      <c r="N13" s="55"/>
       <c r="P13" s="6" t="s">
         <v>110</v>
       </c>
@@ -2700,19 +2695,19 @@
         <f t="shared" si="0"/>
         <v>-155.98000000000002</v>
       </c>
-      <c r="T13" s="54">
+      <c r="T13" s="53">
         <f t="shared" si="1"/>
         <v>-2.7953405017921154</v>
       </c>
-      <c r="U13" s="54"/>
+      <c r="U13" s="53"/>
       <c r="W13" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="X13" s="31">
+      <c r="X13" s="29">
         <f>(C16+C12+C11)/C6</f>
         <v>2.5141625716291308E-2</v>
       </c>
-      <c r="Y13" s="31">
+      <c r="Y13" s="29">
         <f>(D16+D12+D11)/D6</f>
         <v>0.13264661999311361</v>
       </c>
@@ -2720,7 +2715,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="14" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="10" t="s">
         <v>48</v>
       </c>
@@ -2736,11 +2731,11 @@
         <f t="shared" si="4"/>
         <v>-196.98000000000002</v>
       </c>
-      <c r="F14" s="53">
+      <c r="F14" s="52">
         <f t="shared" si="5"/>
         <v>-0.1846266320495637</v>
       </c>
-      <c r="G14" s="53"/>
+      <c r="G14" s="52"/>
       <c r="I14" s="2" t="s">
         <v>72</v>
       </c>
@@ -2754,11 +2749,11 @@
         <f t="shared" ref="L14:L22" si="6">J14-K14</f>
         <v>0</v>
       </c>
-      <c r="M14" s="53">
+      <c r="M14" s="52">
         <f t="shared" ref="M14:M22" si="7">(J14-K14)/ABS(K14)</f>
         <v>0</v>
       </c>
-      <c r="N14" s="53"/>
+      <c r="N14" s="52"/>
       <c r="P14" s="2" t="s">
         <v>111</v>
       </c>
@@ -2772,19 +2767,19 @@
         <f t="shared" si="0"/>
         <v>89.54</v>
       </c>
-      <c r="T14" s="53">
+      <c r="T14" s="52">
         <f t="shared" si="1"/>
         <v>8954</v>
       </c>
-      <c r="U14" s="53"/>
+      <c r="U14" s="52"/>
       <c r="W14" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="X14" s="30">
+      <c r="X14" s="28">
         <f>C18/C6</f>
         <v>-0.42022431554372863</v>
       </c>
-      <c r="Y14" s="30">
+      <c r="Y14" s="28">
         <f>D18/D6</f>
         <v>-0.53062951910937695</v>
       </c>
@@ -2792,7 +2787,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="15" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:26" x14ac:dyDescent="0.3">
       <c r="I15" s="6" t="s">
         <v>73</v>
       </c>
@@ -2806,11 +2801,11 @@
         <f t="shared" si="6"/>
         <v>-44.980000000000018</v>
       </c>
-      <c r="M15" s="54">
+      <c r="M15" s="53">
         <f t="shared" si="7"/>
         <v>-0.14254928059833941</v>
       </c>
-      <c r="N15" s="54"/>
+      <c r="N15" s="53"/>
       <c r="P15" s="6" t="s">
         <v>112</v>
       </c>
@@ -2824,19 +2819,19 @@
         <f t="shared" si="0"/>
         <v>-17.43</v>
       </c>
-      <c r="T15" s="54">
+      <c r="T15" s="53">
         <f t="shared" si="1"/>
         <v>-2.2577720207253886</v>
       </c>
-      <c r="U15" s="54"/>
+      <c r="U15" s="53"/>
       <c r="W15" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="X15" s="31">
+      <c r="X15" s="29">
         <f>C18/J28</f>
         <v>-6.6127507398881971E-2</v>
       </c>
-      <c r="Y15" s="31">
+      <c r="Y15" s="29">
         <f>D18/K28</f>
         <v>-0.11110810713384518</v>
       </c>
@@ -2844,7 +2839,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="16" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="10" t="s">
         <v>49</v>
       </c>
@@ -2860,11 +2855,11 @@
         <f>C16-D16</f>
         <v>112.47000000000003</v>
       </c>
-      <c r="F16" s="53">
+      <c r="F16" s="52">
         <f>(C16-D16)/ABS(D16)</f>
         <v>0.30407981182577659</v>
       </c>
-      <c r="G16" s="53"/>
+      <c r="G16" s="52"/>
       <c r="I16" s="2" t="s">
         <v>74</v>
       </c>
@@ -2878,11 +2873,11 @@
         <f t="shared" si="6"/>
         <v>244.55999999999997</v>
       </c>
-      <c r="M16" s="53">
+      <c r="M16" s="52">
         <f t="shared" si="7"/>
         <v>1.7317660388047018</v>
       </c>
-      <c r="N16" s="53"/>
+      <c r="N16" s="52"/>
       <c r="P16" s="2" t="s">
         <v>113</v>
       </c>
@@ -2896,19 +2891,19 @@
         <f t="shared" si="0"/>
         <v>-0.51</v>
       </c>
-      <c r="T16" s="53">
+      <c r="T16" s="52">
         <f t="shared" si="1"/>
         <v>-0.8793103448275863</v>
       </c>
-      <c r="U16" s="53"/>
+      <c r="U16" s="52"/>
       <c r="W16" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="X16" s="30">
+      <c r="X16" s="28">
         <f>(C16+C11)/(J28+J33)</f>
         <v>-6.0419284308002842E-2</v>
       </c>
-      <c r="Y16" s="30">
+      <c r="Y16" s="28">
         <f>(D16+D11)/(K28+K33)</f>
         <v>-0.10658666110855056</v>
       </c>
@@ -2916,7 +2911,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="17" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="6" t="s">
         <v>50</v>
       </c>
@@ -2946,11 +2941,11 @@
         <f t="shared" si="6"/>
         <v>0.25</v>
       </c>
-      <c r="M17" s="54">
+      <c r="M17" s="53">
         <f t="shared" si="7"/>
         <v>4.5955882352941173E-2</v>
       </c>
-      <c r="N17" s="54"/>
+      <c r="N17" s="53"/>
       <c r="P17" s="12" t="s">
         <v>114</v>
       </c>
@@ -2966,19 +2961,19 @@
         <f t="shared" si="0"/>
         <v>-64.719999999999985</v>
       </c>
-      <c r="T17" s="54">
+      <c r="T17" s="53">
         <f t="shared" si="1"/>
         <v>-0.6627752176139271</v>
       </c>
-      <c r="U17" s="54"/>
+      <c r="U17" s="53"/>
       <c r="W17" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="X17" s="29">
+      <c r="X17" s="27">
         <f>C18/J22</f>
         <v>-5.9393192626383616E-2</v>
       </c>
-      <c r="Y17" s="29">
+      <c r="Y17" s="27">
         <f>D18/K22</f>
         <v>-9.6952269611556618E-2</v>
       </c>
@@ -2986,7 +2981,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="18" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="10" t="s">
         <v>52</v>
       </c>
@@ -3002,11 +2997,11 @@
         <f>C18-D18</f>
         <v>112.47000000000003</v>
       </c>
-      <c r="F18" s="53">
+      <c r="F18" s="52">
         <f>(C18-D18)/ABS(D18)</f>
         <v>0.30407981182577659</v>
       </c>
-      <c r="G18" s="53"/>
+      <c r="G18" s="52"/>
       <c r="I18" s="2" t="s">
         <v>76</v>
       </c>
@@ -3020,11 +3015,11 @@
         <f t="shared" si="6"/>
         <v>0.70000000000000018</v>
       </c>
-      <c r="M18" s="53">
+      <c r="M18" s="52">
         <f t="shared" si="7"/>
         <v>0.11111111111111115</v>
       </c>
-      <c r="N18" s="53"/>
+      <c r="N18" s="52"/>
       <c r="P18" s="2" t="s">
         <v>115</v>
       </c>
@@ -3038,19 +3033,19 @@
         <f t="shared" si="0"/>
         <v>11.24</v>
       </c>
-      <c r="T18" s="53">
+      <c r="T18" s="52">
         <f t="shared" si="1"/>
         <v>3.7095709570957101</v>
       </c>
-      <c r="U18" s="53"/>
-      <c r="W18" s="55" t="s">
+      <c r="U18" s="52"/>
+      <c r="W18" s="51" t="s">
         <v>158</v>
       </c>
-      <c r="X18" s="55"/>
-      <c r="Y18" s="55"/>
-      <c r="Z18" s="55"/>
-    </row>
-    <row r="19" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="X18" s="51"/>
+      <c r="Y18" s="51"/>
+      <c r="Z18" s="51"/>
+    </row>
+    <row r="19" spans="2:26" x14ac:dyDescent="0.3">
       <c r="I19" s="6" t="s">
         <v>77</v>
       </c>
@@ -3064,11 +3059,11 @@
         <f t="shared" si="6"/>
         <v>-8.2100000000000009</v>
       </c>
-      <c r="M19" s="54">
+      <c r="M19" s="53">
         <f t="shared" si="7"/>
         <v>-0.31797056545313712</v>
       </c>
-      <c r="N19" s="54"/>
+      <c r="N19" s="53"/>
       <c r="P19" s="12" t="s">
         <v>116</v>
       </c>
@@ -3084,19 +3079,19 @@
         <f t="shared" si="0"/>
         <v>-53.479999999999983</v>
       </c>
-      <c r="T19" s="54">
+      <c r="T19" s="53">
         <f t="shared" si="1"/>
         <v>-0.56520820122595627</v>
       </c>
-      <c r="U19" s="54"/>
+      <c r="U19" s="53"/>
       <c r="W19" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="X19" s="28">
+      <c r="X19" s="26">
         <f>C4/((K15+J15)/2)</f>
         <v>1.9378604333731444</v>
       </c>
-      <c r="Y19" s="28">
+      <c r="Y19" s="26">
         <f>D4/((L15+K15)/2)</f>
         <v>5.0683027794204607</v>
       </c>
@@ -3104,7 +3099,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="20" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="2" t="s">
         <v>53</v>
       </c>
@@ -3118,11 +3113,11 @@
         <f>C20-D20</f>
         <v>1.0000000000000002E-2</v>
       </c>
-      <c r="F20" s="53">
+      <c r="F20" s="52">
         <f>(C20-D20)/ABS(D20)</f>
         <v>0.20000000000000004</v>
       </c>
-      <c r="G20" s="53"/>
+      <c r="G20" s="52"/>
       <c r="I20" s="2" t="s">
         <v>78</v>
       </c>
@@ -3136,19 +3131,19 @@
         <f t="shared" si="6"/>
         <v>-33.549999999999997</v>
       </c>
-      <c r="M20" s="53">
+      <c r="M20" s="52">
         <f t="shared" si="7"/>
         <v>-0.31561618062088426</v>
       </c>
-      <c r="N20" s="53"/>
+      <c r="N20" s="52"/>
       <c r="W20" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="X20" s="33">
+      <c r="X20" s="31">
         <f>365/X19</f>
         <v>188.352057616792</v>
       </c>
-      <c r="Y20" s="33">
+      <c r="Y20" s="31">
         <f>365/Y19</f>
         <v>72.016218423662565</v>
       </c>
@@ -3156,7 +3151,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="21" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="12" t="s">
         <v>54</v>
       </c>
@@ -3172,11 +3167,11 @@
         <f>C21-D21</f>
         <v>112.48000000000002</v>
       </c>
-      <c r="F21" s="54">
+      <c r="F21" s="53">
         <f>(C21-D21)/ABS(D21)</f>
         <v>0.30406574394463665</v>
       </c>
-      <c r="G21" s="54"/>
+      <c r="G21" s="53"/>
       <c r="I21" s="12" t="s">
         <v>79</v>
       </c>
@@ -3192,27 +3187,27 @@
         <f t="shared" si="6"/>
         <v>158.76999999999998</v>
       </c>
-      <c r="M21" s="54">
+      <c r="M21" s="53">
         <f t="shared" si="7"/>
         <v>0.26433470964304739</v>
       </c>
-      <c r="N21" s="54"/>
-      <c r="P21" s="55" t="s">
+      <c r="N21" s="53"/>
+      <c r="P21" s="51" t="s">
         <v>117</v>
       </c>
-      <c r="Q21" s="55"/>
-      <c r="R21" s="55"/>
-      <c r="S21" s="55"/>
-      <c r="T21" s="55"/>
-      <c r="U21" s="55"/>
+      <c r="Q21" s="51"/>
+      <c r="R21" s="51"/>
+      <c r="S21" s="51"/>
+      <c r="T21" s="51"/>
+      <c r="U21" s="51"/>
       <c r="W21" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="X21" s="28">
+      <c r="X21" s="26">
         <f>C4/(J21-J41)</f>
         <v>1.2120416613309428</v>
       </c>
-      <c r="Y21" s="28">
+      <c r="Y21" s="26">
         <f>D4/(K21-K41)</f>
         <v>3.5714136889259303</v>
       </c>
@@ -3220,7 +3215,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="22" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:26" x14ac:dyDescent="0.3">
       <c r="I22" s="10" t="s">
         <v>80</v>
       </c>
@@ -3236,11 +3231,11 @@
         <f t="shared" si="6"/>
         <v>518.86000000000013</v>
       </c>
-      <c r="M22" s="53">
+      <c r="M22" s="52">
         <f t="shared" si="7"/>
         <v>0.136006311976241</v>
       </c>
-      <c r="N22" s="53"/>
+      <c r="N22" s="52"/>
       <c r="P22" s="2" t="s">
         <v>118</v>
       </c>
@@ -3254,19 +3249,19 @@
         <f t="shared" ref="S22:S27" si="8">Q22-R22</f>
         <v>-214.78000000000003</v>
       </c>
-      <c r="T22" s="53">
+      <c r="T22" s="52">
         <f t="shared" ref="T22:T27" si="9">(Q22-R22)/ABS(R22)</f>
         <v>-2.1732267530102201</v>
       </c>
-      <c r="U22" s="53"/>
+      <c r="U22" s="52"/>
       <c r="W22" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="X22" s="27">
+      <c r="X22" s="25">
         <f>C4/J22</f>
         <v>0.13103651966043892</v>
       </c>
-      <c r="Y22" s="27">
+      <c r="Y22" s="25">
         <f>D4/K22</f>
         <v>0.17972356270167264</v>
       </c>
@@ -3274,15 +3269,15 @@
         <v>166</v>
       </c>
     </row>
-    <row r="23" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="55" t="s">
+    <row r="23" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="51" t="s">
         <v>55</v>
       </c>
-      <c r="C23" s="55"/>
-      <c r="D23" s="55"/>
-      <c r="E23" s="55"/>
-      <c r="F23" s="55"/>
-      <c r="G23" s="55"/>
+      <c r="C23" s="51"/>
+      <c r="D23" s="51"/>
+      <c r="E23" s="51"/>
+      <c r="F23" s="51"/>
+      <c r="G23" s="51"/>
       <c r="P23" s="6" t="s">
         <v>119</v>
       </c>
@@ -3296,19 +3291,19 @@
         <f t="shared" si="8"/>
         <v>137.90000000000003</v>
       </c>
-      <c r="T23" s="54">
+      <c r="T23" s="53">
         <f t="shared" si="9"/>
         <v>0.31020132718479371</v>
       </c>
-      <c r="U23" s="54"/>
-      <c r="W23" s="55" t="s">
+      <c r="U23" s="53"/>
+      <c r="W23" s="51" t="s">
         <v>167</v>
       </c>
-      <c r="X23" s="55"/>
-      <c r="Y23" s="55"/>
-      <c r="Z23" s="55"/>
-    </row>
-    <row r="24" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="X23" s="51"/>
+      <c r="Y23" s="51"/>
+      <c r="Z23" s="51"/>
+    </row>
+    <row r="24" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="1" t="s">
         <v>56</v>
       </c>
@@ -3321,16 +3316,16 @@
       <c r="E24" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="F24" s="56"/>
-      <c r="G24" s="56"/>
-      <c r="I24" s="55" t="s">
+      <c r="F24" s="54"/>
+      <c r="G24" s="54"/>
+      <c r="I24" s="51" t="s">
         <v>81</v>
       </c>
-      <c r="J24" s="55"/>
-      <c r="K24" s="55"/>
-      <c r="L24" s="55"/>
-      <c r="M24" s="55"/>
-      <c r="N24" s="55"/>
+      <c r="J24" s="51"/>
+      <c r="K24" s="51"/>
+      <c r="L24" s="51"/>
+      <c r="M24" s="51"/>
+      <c r="N24" s="51"/>
       <c r="P24" s="2" t="s">
         <v>120</v>
       </c>
@@ -3344,25 +3339,25 @@
         <f t="shared" si="8"/>
         <v>-5.2700000000000005</v>
       </c>
-      <c r="T24" s="53">
+      <c r="T24" s="52">
         <f t="shared" si="9"/>
         <v>-0.84455128205128205</v>
       </c>
-      <c r="U24" s="53"/>
+      <c r="U24" s="52"/>
       <c r="W24" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="X24" s="26">
+      <c r="X24" s="3">
         <v>19017.05</v>
       </c>
-      <c r="Y24" s="26">
+      <c r="Y24" s="3">
         <v>18759.61</v>
       </c>
       <c r="Z24" s="14" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="25" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="6" t="s">
         <v>58</v>
       </c>
@@ -3378,16 +3373,16 @@
         <f>C25-D25</f>
         <v>-6.8865023761620792E-2</v>
       </c>
-      <c r="F25" s="52"/>
-      <c r="G25" s="52"/>
-      <c r="I25" s="58" t="s">
+      <c r="F25" s="56"/>
+      <c r="G25" s="56"/>
+      <c r="I25" s="55" t="s">
         <v>82</v>
       </c>
-      <c r="J25" s="58"/>
-      <c r="K25" s="58"/>
-      <c r="L25" s="58"/>
-      <c r="M25" s="58"/>
-      <c r="N25" s="58"/>
+      <c r="J25" s="55"/>
+      <c r="K25" s="55"/>
+      <c r="L25" s="55"/>
+      <c r="M25" s="55"/>
+      <c r="N25" s="55"/>
       <c r="P25" s="6" t="s">
         <v>121</v>
       </c>
@@ -3401,19 +3396,19 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="T25" s="54">
+      <c r="T25" s="53">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="U25" s="54"/>
+      <c r="U25" s="53"/>
       <c r="W25" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="X25" s="25">
+      <c r="X25" s="7">
         <f>J28</f>
         <v>3892.4799999999996</v>
       </c>
-      <c r="Y25" s="25">
+      <c r="Y25" s="7">
         <f>K28</f>
         <v>3328.9200000000019</v>
       </c>
@@ -3421,7 +3416,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="26" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="2" t="s">
         <v>59</v>
       </c>
@@ -3437,8 +3432,8 @@
         <f>C26-D26</f>
         <v>-0.10750499427682231</v>
       </c>
-      <c r="F26" s="52"/>
-      <c r="G26" s="52"/>
+      <c r="F26" s="56"/>
+      <c r="G26" s="56"/>
       <c r="I26" s="2" t="s">
         <v>83</v>
       </c>
@@ -3452,11 +3447,11 @@
         <f>J26-K26</f>
         <v>821</v>
       </c>
-      <c r="M26" s="53">
+      <c r="M26" s="52">
         <f>(J26-K26)/ABS(K26)</f>
         <v>3.7238288762291807E-2</v>
       </c>
-      <c r="N26" s="53"/>
+      <c r="N26" s="52"/>
       <c r="P26" s="2" t="s">
         <v>122</v>
       </c>
@@ -3470,25 +3465,25 @@
         <f t="shared" si="8"/>
         <v>4.13</v>
       </c>
-      <c r="T26" s="53">
+      <c r="T26" s="52">
         <f t="shared" si="9"/>
         <v>0.58498583569405105</v>
       </c>
-      <c r="U26" s="53"/>
+      <c r="U26" s="52"/>
       <c r="W26" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="X26" s="26">
+      <c r="X26" s="3">
         <v>821</v>
       </c>
-      <c r="Y26" s="26">
+      <c r="Y26" s="3">
         <v>546</v>
       </c>
       <c r="Z26" s="14" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="27" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="6" t="s">
         <v>60</v>
       </c>
@@ -3504,8 +3499,8 @@
         <f>C27-D27</f>
         <v>0.11040520356564831</v>
       </c>
-      <c r="F27" s="52"/>
-      <c r="G27" s="52"/>
+      <c r="F27" s="56"/>
+      <c r="G27" s="56"/>
       <c r="I27" s="6" t="s">
         <v>84</v>
       </c>
@@ -3519,11 +3514,11 @@
         <f>J27-K27</f>
         <v>-257.44000000000233</v>
       </c>
-      <c r="M27" s="54">
+      <c r="M27" s="53">
         <f>(J27-K27)/ABS(K27)</f>
         <v>-1.3753400419269417E-2</v>
       </c>
-      <c r="N27" s="54"/>
+      <c r="N27" s="53"/>
       <c r="P27" s="12" t="s">
         <v>123</v>
       </c>
@@ -3539,25 +3534,25 @@
         <f t="shared" si="8"/>
         <v>-78.019999999999868</v>
       </c>
-      <c r="T27" s="54">
+      <c r="T27" s="53">
         <f t="shared" si="9"/>
         <v>-0.14721865801192516</v>
       </c>
-      <c r="U27" s="54"/>
+      <c r="U27" s="53"/>
       <c r="W27" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="X27" s="25">
+      <c r="X27" s="7">
         <v>2.2799999999999998</v>
       </c>
-      <c r="Y27" s="25">
+      <c r="Y27" s="7">
         <v>82.99</v>
       </c>
       <c r="Z27" s="15" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="28" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:26" x14ac:dyDescent="0.3">
       <c r="I28" s="10" t="s">
         <v>85</v>
       </c>
@@ -3573,32 +3568,32 @@
         <f>J28-K28</f>
         <v>563.55999999999767</v>
       </c>
-      <c r="M28" s="53">
+      <c r="M28" s="52">
         <f>(J28-K28)/ABS(K28)</f>
         <v>0.16929214279706251</v>
       </c>
-      <c r="N28" s="53"/>
-    </row>
-    <row r="29" spans="2:26" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N28" s="52"/>
+    </row>
+    <row r="29" spans="2:26" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="13"/>
-      <c r="P29" s="55" t="s">
+      <c r="P29" s="51" t="s">
         <v>124</v>
       </c>
-      <c r="Q29" s="55"/>
-      <c r="R29" s="55"/>
-      <c r="S29" s="55"/>
-      <c r="T29" s="55"/>
-      <c r="U29" s="55"/>
-    </row>
-    <row r="30" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="I30" s="58" t="s">
+      <c r="Q29" s="51"/>
+      <c r="R29" s="51"/>
+      <c r="S29" s="51"/>
+      <c r="T29" s="51"/>
+      <c r="U29" s="51"/>
+    </row>
+    <row r="30" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="I30" s="55" t="s">
         <v>86</v>
       </c>
-      <c r="J30" s="58"/>
-      <c r="K30" s="58"/>
-      <c r="L30" s="58"/>
-      <c r="M30" s="58"/>
-      <c r="N30" s="58"/>
+      <c r="J30" s="55"/>
+      <c r="K30" s="55"/>
+      <c r="L30" s="55"/>
+      <c r="M30" s="55"/>
+      <c r="N30" s="55"/>
       <c r="P30" s="2" t="s">
         <v>125</v>
       </c>
@@ -3612,13 +3607,13 @@
         <f>Q30-R30</f>
         <v>0.35000000000000142</v>
       </c>
-      <c r="T30" s="53">
+      <c r="T30" s="52">
         <f>(Q30-R30)/ABS(R30)</f>
         <v>2.8455284552845642E-2</v>
       </c>
-      <c r="U30" s="53"/>
-    </row>
-    <row r="31" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="U30" s="52"/>
+    </row>
+    <row r="31" spans="2:26" x14ac:dyDescent="0.3">
       <c r="I31" s="6" t="s">
         <v>87</v>
       </c>
@@ -3632,11 +3627,11 @@
         <f>J31-K31</f>
         <v>71.060000000000016</v>
       </c>
-      <c r="M31" s="54">
+      <c r="M31" s="53">
         <f>(J31-K31)/ABS(K31)</f>
         <v>1.1181746656176241</v>
       </c>
-      <c r="N31" s="54"/>
+      <c r="N31" s="53"/>
       <c r="P31" s="6" t="s">
         <v>126</v>
       </c>
@@ -3650,13 +3645,13 @@
         <f>Q31-R31</f>
         <v>275</v>
       </c>
-      <c r="T31" s="54">
+      <c r="T31" s="53">
         <f>(Q31-R31)/ABS(R31)</f>
         <v>0.50366300366300365</v>
       </c>
-      <c r="U31" s="54"/>
-    </row>
-    <row r="32" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="U31" s="53"/>
+    </row>
+    <row r="32" spans="2:26" x14ac:dyDescent="0.3">
       <c r="I32" s="2" t="s">
         <v>88</v>
       </c>
@@ -3670,11 +3665,11 @@
         <f>J32-K32</f>
         <v>2.0299999999999994</v>
       </c>
-      <c r="M32" s="53">
+      <c r="M32" s="52">
         <f>(J32-K32)/ABS(K32)</f>
         <v>0.14541547277936956</v>
       </c>
-      <c r="N32" s="53"/>
+      <c r="N32" s="52"/>
       <c r="P32" s="10" t="s">
         <v>127</v>
       </c>
@@ -3690,13 +3685,13 @@
         <f>Q32-R32</f>
         <v>275.34999999999991</v>
       </c>
-      <c r="T32" s="53">
+      <c r="T32" s="52">
         <f>(Q32-R32)/ABS(R32)</f>
         <v>0.51592655049653346</v>
       </c>
-      <c r="U32" s="53"/>
-    </row>
-    <row r="33" spans="9:21" x14ac:dyDescent="0.25">
+      <c r="U32" s="52"/>
+    </row>
+    <row r="33" spans="9:21" x14ac:dyDescent="0.3">
       <c r="I33" s="12" t="s">
         <v>89</v>
       </c>
@@ -3712,13 +3707,13 @@
         <f>J33-K33</f>
         <v>73.090000000000032</v>
       </c>
-      <c r="M33" s="54">
+      <c r="M33" s="53">
         <f>(J33-K33)/ABS(K33)</f>
         <v>0.94297509998709894</v>
       </c>
-      <c r="N33" s="54"/>
-    </row>
-    <row r="34" spans="9:21" x14ac:dyDescent="0.25">
+      <c r="N33" s="53"/>
+    </row>
+    <row r="34" spans="9:21" x14ac:dyDescent="0.3">
       <c r="P34" s="10" t="s">
         <v>128</v>
       </c>
@@ -3734,21 +3729,21 @@
         <f>Q34-R34</f>
         <v>143.85000000000002</v>
       </c>
-      <c r="T34" s="53">
+      <c r="T34" s="52">
         <f>(Q34-R34)/ABS(R34)</f>
         <v>1.4624847498983327</v>
       </c>
-      <c r="U34" s="53"/>
-    </row>
-    <row r="35" spans="9:21" x14ac:dyDescent="0.25">
-      <c r="I35" s="58" t="s">
+      <c r="U34" s="52"/>
+    </row>
+    <row r="35" spans="9:21" x14ac:dyDescent="0.3">
+      <c r="I35" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="J35" s="58"/>
-      <c r="K35" s="58"/>
-      <c r="L35" s="58"/>
-      <c r="M35" s="58"/>
-      <c r="N35" s="58"/>
+      <c r="J35" s="55"/>
+      <c r="K35" s="55"/>
+      <c r="L35" s="55"/>
+      <c r="M35" s="55"/>
+      <c r="N35" s="55"/>
       <c r="P35" s="6" t="s">
         <v>129</v>
       </c>
@@ -3762,13 +3757,13 @@
         <f>Q35-R35</f>
         <v>102.38</v>
       </c>
-      <c r="T35" s="54">
+      <c r="T35" s="53">
         <f>(Q35-R35)/ABS(R35)</f>
         <v>2.3121047877145435</v>
       </c>
-      <c r="U35" s="54"/>
-    </row>
-    <row r="36" spans="9:21" x14ac:dyDescent="0.25">
+      <c r="U35" s="53"/>
+    </row>
+    <row r="36" spans="9:21" x14ac:dyDescent="0.3">
       <c r="I36" s="2" t="s">
         <v>91</v>
       </c>
@@ -3782,11 +3777,11 @@
         <f t="shared" ref="L36:L43" si="10">J36-K36</f>
         <v>19.64</v>
       </c>
-      <c r="M36" s="53">
+      <c r="M36" s="52">
         <f t="shared" ref="M36:M43" si="11">(J36-K36)/ABS(K36)</f>
         <v>2.2548794489092994</v>
       </c>
-      <c r="N36" s="53"/>
+      <c r="N36" s="52"/>
       <c r="P36" s="10" t="s">
         <v>130</v>
       </c>
@@ -3802,13 +3797,13 @@
         <f>Q36-R36</f>
         <v>246.23</v>
       </c>
-      <c r="T36" s="53">
+      <c r="T36" s="52">
         <f>(Q36-R36)/ABS(R36)</f>
         <v>1.7262338754907456</v>
       </c>
-      <c r="U36" s="53"/>
-    </row>
-    <row r="37" spans="9:21" x14ac:dyDescent="0.25">
+      <c r="U36" s="52"/>
+    </row>
+    <row r="37" spans="9:21" x14ac:dyDescent="0.3">
       <c r="I37" s="6" t="s">
         <v>92</v>
       </c>
@@ -3822,13 +3817,13 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="M37" s="54">
+      <c r="M37" s="53">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="N37" s="54"/>
-    </row>
-    <row r="38" spans="9:21" x14ac:dyDescent="0.25">
+      <c r="N37" s="53"/>
+    </row>
+    <row r="38" spans="9:21" x14ac:dyDescent="0.3">
       <c r="I38" s="2" t="s">
         <v>93</v>
       </c>
@@ -3842,13 +3837,13 @@
         <f t="shared" si="10"/>
         <v>-127.79000000000002</v>
       </c>
-      <c r="M38" s="53">
+      <c r="M38" s="52">
         <f t="shared" si="11"/>
         <v>-0.33543323621282517</v>
       </c>
-      <c r="N38" s="53"/>
-    </row>
-    <row r="39" spans="9:21" x14ac:dyDescent="0.25">
+      <c r="N38" s="52"/>
+    </row>
+    <row r="39" spans="9:21" x14ac:dyDescent="0.3">
       <c r="I39" s="6" t="s">
         <v>94</v>
       </c>
@@ -3862,13 +3857,13 @@
         <f t="shared" si="10"/>
         <v>-9.7100000000000009</v>
       </c>
-      <c r="M39" s="54">
+      <c r="M39" s="53">
         <f t="shared" si="11"/>
         <v>-0.57421643997634542</v>
       </c>
-      <c r="N39" s="54"/>
-    </row>
-    <row r="40" spans="9:21" x14ac:dyDescent="0.25">
+      <c r="N39" s="53"/>
+    </row>
+    <row r="40" spans="9:21" x14ac:dyDescent="0.3">
       <c r="I40" s="2" t="s">
         <v>95</v>
       </c>
@@ -3882,13 +3877,13 @@
         <f t="shared" si="10"/>
         <v>6.999999999999984E-2</v>
       </c>
-      <c r="M40" s="53">
+      <c r="M40" s="52">
         <f t="shared" si="11"/>
         <v>3.4653465346534573E-2</v>
       </c>
-      <c r="N40" s="53"/>
-    </row>
-    <row r="41" spans="9:21" x14ac:dyDescent="0.25">
+      <c r="N40" s="52"/>
+    </row>
+    <row r="41" spans="9:21" x14ac:dyDescent="0.3">
       <c r="I41" s="12" t="s">
         <v>96</v>
       </c>
@@ -3904,13 +3899,13 @@
         <f t="shared" si="10"/>
         <v>-117.79000000000008</v>
       </c>
-      <c r="M41" s="54">
+      <c r="M41" s="53">
         <f t="shared" si="11"/>
         <v>-0.28823471834777092</v>
       </c>
-      <c r="N41" s="54"/>
-    </row>
-    <row r="42" spans="9:21" x14ac:dyDescent="0.25">
+      <c r="N41" s="53"/>
+    </row>
+    <row r="42" spans="9:21" x14ac:dyDescent="0.3">
       <c r="I42" s="10" t="s">
         <v>97</v>
       </c>
@@ -3926,13 +3921,13 @@
         <f t="shared" si="10"/>
         <v>-44.700000000000045</v>
       </c>
-      <c r="M42" s="53">
+      <c r="M42" s="52">
         <f t="shared" si="11"/>
         <v>-9.1943147458707949E-2</v>
       </c>
-      <c r="N42" s="53"/>
-    </row>
-    <row r="43" spans="9:21" x14ac:dyDescent="0.25">
+      <c r="N42" s="52"/>
+    </row>
+    <row r="43" spans="9:21" x14ac:dyDescent="0.3">
       <c r="I43" s="12" t="s">
         <v>98</v>
       </c>
@@ -3948,44 +3943,74 @@
         <f t="shared" si="10"/>
         <v>518.85999999999785</v>
       </c>
-      <c r="M43" s="54">
+      <c r="M43" s="53">
         <f t="shared" si="11"/>
         <v>0.13600203402803016</v>
       </c>
-      <c r="N43" s="54"/>
-    </row>
-    <row r="45" spans="9:21" x14ac:dyDescent="0.25">
+      <c r="N43" s="53"/>
+    </row>
+    <row r="45" spans="9:21" x14ac:dyDescent="0.3">
       <c r="I45" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="100">
-    <mergeCell ref="W23:Z23"/>
-    <mergeCell ref="W1:Z1"/>
-    <mergeCell ref="W3:Z3"/>
-    <mergeCell ref="W7:Z7"/>
-    <mergeCell ref="W11:Z11"/>
-    <mergeCell ref="W18:Z18"/>
-    <mergeCell ref="T36:U36"/>
-    <mergeCell ref="T27:U27"/>
-    <mergeCell ref="P29:U29"/>
-    <mergeCell ref="T30:U30"/>
-    <mergeCell ref="T31:U31"/>
-    <mergeCell ref="T32:U32"/>
-    <mergeCell ref="T24:U24"/>
-    <mergeCell ref="T25:U25"/>
-    <mergeCell ref="T26:U26"/>
-    <mergeCell ref="T34:U34"/>
-    <mergeCell ref="T35:U35"/>
-    <mergeCell ref="T18:U18"/>
-    <mergeCell ref="T19:U19"/>
-    <mergeCell ref="P21:U21"/>
-    <mergeCell ref="T22:U22"/>
-    <mergeCell ref="T23:U23"/>
-    <mergeCell ref="T13:U13"/>
-    <mergeCell ref="T14:U14"/>
-    <mergeCell ref="T15:U15"/>
-    <mergeCell ref="T16:U16"/>
-    <mergeCell ref="T17:U17"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="B23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="B8:G8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="I1:N1"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="I3:N3"/>
+    <mergeCell ref="I4:N4"/>
+    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="M9:N9"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="I13:N13"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="M19:N19"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="I24:N24"/>
+    <mergeCell ref="I25:N25"/>
+    <mergeCell ref="M26:N26"/>
+    <mergeCell ref="M27:N27"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="I30:N30"/>
+    <mergeCell ref="M31:N31"/>
+    <mergeCell ref="M32:N32"/>
+    <mergeCell ref="M33:N33"/>
+    <mergeCell ref="I35:N35"/>
+    <mergeCell ref="M36:N36"/>
+    <mergeCell ref="M37:N37"/>
+    <mergeCell ref="M38:N38"/>
+    <mergeCell ref="M39:N39"/>
     <mergeCell ref="M40:N40"/>
     <mergeCell ref="M41:N41"/>
     <mergeCell ref="M42:N42"/>
@@ -4002,63 +4027,33 @@
     <mergeCell ref="T10:U10"/>
     <mergeCell ref="T11:U11"/>
     <mergeCell ref="T12:U12"/>
-    <mergeCell ref="I35:N35"/>
-    <mergeCell ref="M36:N36"/>
-    <mergeCell ref="M37:N37"/>
-    <mergeCell ref="M38:N38"/>
-    <mergeCell ref="M39:N39"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="I30:N30"/>
-    <mergeCell ref="M31:N31"/>
-    <mergeCell ref="M32:N32"/>
-    <mergeCell ref="M33:N33"/>
-    <mergeCell ref="M22:N22"/>
-    <mergeCell ref="I24:N24"/>
-    <mergeCell ref="I25:N25"/>
-    <mergeCell ref="M26:N26"/>
-    <mergeCell ref="M27:N27"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="M19:N19"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="I13:N13"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="M9:N9"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="I1:N1"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="I3:N3"/>
-    <mergeCell ref="I4:N4"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="B8:G8"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="B23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="T13:U13"/>
+    <mergeCell ref="T14:U14"/>
+    <mergeCell ref="T15:U15"/>
+    <mergeCell ref="T16:U16"/>
+    <mergeCell ref="T17:U17"/>
+    <mergeCell ref="T18:U18"/>
+    <mergeCell ref="T19:U19"/>
+    <mergeCell ref="P21:U21"/>
+    <mergeCell ref="T22:U22"/>
+    <mergeCell ref="T23:U23"/>
+    <mergeCell ref="T24:U24"/>
+    <mergeCell ref="T25:U25"/>
+    <mergeCell ref="T26:U26"/>
+    <mergeCell ref="T34:U34"/>
+    <mergeCell ref="T35:U35"/>
+    <mergeCell ref="T36:U36"/>
+    <mergeCell ref="T27:U27"/>
+    <mergeCell ref="P29:U29"/>
+    <mergeCell ref="T30:U30"/>
+    <mergeCell ref="T31:U31"/>
+    <mergeCell ref="T32:U32"/>
+    <mergeCell ref="W23:Z23"/>
+    <mergeCell ref="W1:Z1"/>
+    <mergeCell ref="W3:Z3"/>
+    <mergeCell ref="W7:Z7"/>
+    <mergeCell ref="W11:Z11"/>
+    <mergeCell ref="W18:Z18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -4066,32 +4061,32 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B1:C58"/>
-  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="49.140625" customWidth="1"/>
-    <col min="3" max="3" width="58.5703125" customWidth="1"/>
+    <col min="2" max="2" width="70.77734375" customWidth="1"/>
+    <col min="3" max="3" width="73.21875" customWidth="1"/>
     <col min="4" max="4" width="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="57" t="s">
+    <row r="1" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="42" t="s">
         <v>176</v>
       </c>
-      <c r="C1" s="57"/>
-    </row>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C1" s="42"/>
+    </row>
+    <row r="2" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B2" s="13"/>
     </row>
-    <row r="4" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="59" t="s">
+    <row r="4" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="41" t="s">
         <v>177</v>
       </c>
-      <c r="C4" s="59"/>
-    </row>
-    <row r="5" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C4" s="41"/>
+    </row>
+    <row r="5" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="17" t="s">
         <v>178</v>
       </c>
@@ -4099,7 +4094,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="6" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="18" t="s">
         <v>180</v>
       </c>
@@ -4107,15 +4102,15 @@
         <v>181</v>
       </c>
     </row>
-    <row r="7" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="18" t="s">
         <v>182</v>
       </c>
-      <c r="C7" s="43" t="s">
+      <c r="C7" s="40" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="8" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="18" t="s">
         <v>183</v>
       </c>
@@ -4123,7 +4118,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="9" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="18" t="s">
         <v>185</v>
       </c>
@@ -4131,7 +4126,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="10" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="18" t="s">
         <v>187</v>
       </c>
@@ -4139,7 +4134,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="11" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="18" t="s">
         <v>189</v>
       </c>
@@ -4147,13 +4142,13 @@
         <v>190</v>
       </c>
     </row>
-    <row r="13" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="59" t="s">
+    <row r="13" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="41" t="s">
         <v>191</v>
       </c>
-      <c r="C13" s="59"/>
-    </row>
-    <row r="14" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C13" s="41"/>
+    </row>
+    <row r="14" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="17" t="s">
         <v>192</v>
       </c>
@@ -4161,7 +4156,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="15" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="20" t="s">
         <v>194</v>
       </c>
@@ -4169,7 +4164,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="16" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="20" t="s">
         <v>196</v>
       </c>
@@ -4177,7 +4172,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="17" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="20" t="s">
         <v>198</v>
       </c>
@@ -4185,7 +4180,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="18" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="20" t="s">
         <v>200</v>
       </c>
@@ -4193,7 +4188,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="19" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="20" t="s">
         <v>202</v>
       </c>
@@ -4201,7 +4196,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="20" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="20" t="s">
         <v>204</v>
       </c>
@@ -4209,13 +4204,13 @@
         <v>205</v>
       </c>
     </row>
-    <row r="22" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="59" t="s">
+    <row r="22" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="41" t="s">
         <v>206</v>
       </c>
-      <c r="C22" s="59"/>
-    </row>
-    <row r="23" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C22" s="41"/>
+    </row>
+    <row r="23" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="17" t="s">
         <v>207</v>
       </c>
@@ -4223,7 +4218,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="24" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="18" t="s">
         <v>209</v>
       </c>
@@ -4231,7 +4226,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="25" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="18" t="s">
         <v>211</v>
       </c>
@@ -4239,7 +4234,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="26" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="18" t="s">
         <v>213</v>
       </c>
@@ -4247,7 +4242,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="27" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="18" t="s">
         <v>215</v>
       </c>
@@ -4255,7 +4250,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="28" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="18" t="s">
         <v>217</v>
       </c>
@@ -4263,13 +4258,13 @@
         <v>218</v>
       </c>
     </row>
-    <row r="30" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="59" t="s">
+    <row r="30" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B30" s="41" t="s">
         <v>219</v>
       </c>
-      <c r="C30" s="59"/>
-    </row>
-    <row r="31" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C30" s="41"/>
+    </row>
+    <row r="31" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="17" t="s">
         <v>220</v>
       </c>
@@ -4277,7 +4272,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="32" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="22" t="s">
         <v>222</v>
       </c>
@@ -4285,7 +4280,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="33" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="22" t="s">
         <v>224</v>
       </c>
@@ -4293,7 +4288,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="34" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="22" t="s">
         <v>226</v>
       </c>
@@ -4301,7 +4296,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="35" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="22" t="s">
         <v>228</v>
       </c>
@@ -4309,7 +4304,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="36" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="22" t="s">
         <v>230</v>
       </c>
@@ -4317,7 +4312,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="37" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="22" t="s">
         <v>232</v>
       </c>
@@ -4325,13 +4320,13 @@
         <v>233</v>
       </c>
     </row>
-    <row r="39" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="59" t="s">
+    <row r="39" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B39" s="41" t="s">
         <v>234</v>
       </c>
-      <c r="C39" s="59"/>
-    </row>
-    <row r="40" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C39" s="41"/>
+    </row>
+    <row r="40" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="17" t="s">
         <v>235</v>
       </c>
@@ -4339,7 +4334,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="41" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="24" t="s">
         <v>237</v>
       </c>
@@ -4347,7 +4342,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="42" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="24" t="s">
         <v>239</v>
       </c>
@@ -4355,7 +4350,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="43" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="24" t="s">
         <v>241</v>
       </c>
@@ -4363,7 +4358,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="44" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="24" t="s">
         <v>243</v>
       </c>
@@ -4371,7 +4366,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="45" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="24" t="s">
         <v>245</v>
       </c>
@@ -4379,7 +4374,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="46" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="24" t="s">
         <v>247</v>
       </c>
@@ -4387,7 +4382,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="47" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="24" t="s">
         <v>249</v>
       </c>
@@ -4395,13 +4390,13 @@
         <v>250</v>
       </c>
     </row>
-    <row r="49" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="59" t="s">
+    <row r="49" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B49" s="41" t="s">
         <v>251</v>
       </c>
-      <c r="C49" s="59"/>
-    </row>
-    <row r="50" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C49" s="41"/>
+    </row>
+    <row r="50" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="17" t="s">
         <v>252</v>
       </c>
@@ -4409,7 +4404,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="51" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="19" t="s">
         <v>254</v>
       </c>
@@ -4417,7 +4412,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="52" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="19" t="s">
         <v>256</v>
       </c>
@@ -4425,7 +4420,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="53" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="19" t="s">
         <v>258</v>
       </c>
@@ -4433,7 +4428,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="54" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="19" t="s">
         <v>260</v>
       </c>
@@ -4441,7 +4436,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="55" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" s="19" t="s">
         <v>262</v>
       </c>
@@ -4449,7 +4444,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="56" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" s="19" t="s">
         <v>264</v>
       </c>
@@ -4457,7 +4452,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="58" spans="2:3" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:3" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B58" s="13"/>
     </row>
   </sheetData>
